--- a/Semiconductor_WC_Benchmarking.xlsx
+++ b/Semiconductor_WC_Benchmarking.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Scoring_Ranking" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Benchmark_Analysis" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Cash_Release" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +64,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +101,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -119,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,6 +160,9 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -163,6 +172,9 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -170,6 +182,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +203,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1038,7 +1065,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Sources: AMD/Intel/TXN/NVIDIA/Qualcomm/NXP/Micron → SEC EDGAR 10-K FY2023. TSMC → 20-F (TWD→USD @31.2). STMicro/Infineon → 20-F / Annual Report (EUR→USD @1.065). NVIDIA FY ends Jan-2024 | Qualcomm &amp; Infineon FY end Sep-2023 | Micron FY ends Aug-2023.</t>
+          <t>Sources: AMD/Intel/TXN/NVIDIA/Qualcomm/NXP/Micron → SEC EDGAR 10-K FY2023.  TSMC → 20-F (TWD→USD @31.2).  STMicro/Infineon → 20-F/Annual Report (EUR→USD @1.065).  NVIDIA FY ends Jan-2024 | Qualcomm &amp; Infineon FY end Sep-2023 | Micron FY ends Aug-2023.</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1071,8 +1098,10 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1082,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
+    <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Company</t>
@@ -1106,7 +1135,7 @@
         <is>
           <t>Working Capital
 ($M)
-[=TCA – TCL]</t>
+[=TCA–TCL]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1160,12 +1189,26 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Current Ratio
+[=TCA÷TCL]
+(≥1 healthy)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Quick Ratio
+[=(TCA–Inv)÷TCL]
+(≥0.8 healthy)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>WC/Rev
 Rank
 (1=Best)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>NWC/Rev
 Rank
@@ -1219,16 +1262,24 @@
         <v/>
       </c>
       <c r="L3" s="12">
+        <f>B3/C3</f>
+        <v/>
+      </c>
+      <c r="M3" s="12">
+        <f>(B3-H3)/C3</f>
+        <v/>
+      </c>
+      <c r="N3" s="13">
         <f>RANK(F3,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M3" s="12">
+      <c r="O3" s="13">
         <f>RANK(K3,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <f>Raw_Data!A4</f>
         <v/>
       </c>
@@ -1248,7 +1299,7 @@
         <f>Raw_Data!B4</f>
         <v/>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="15">
         <f>D4/E4</f>
         <v/>
       </c>
@@ -1268,15 +1319,23 @@
         <f>G4+H4-I4</f>
         <v/>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="15">
         <f>J4/E4</f>
         <v/>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="16">
+        <f>B4/C4</f>
+        <v/>
+      </c>
+      <c r="M4" s="16">
+        <f>(B4-H4)/C4</f>
+        <v/>
+      </c>
+      <c r="N4" s="17">
         <f>RANK(F4,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M4" s="15">
+      <c r="O4" s="17">
         <f>RANK(K4,$K$3:$K$12,1)</f>
         <v/>
       </c>
@@ -1327,16 +1386,24 @@
         <v/>
       </c>
       <c r="L5" s="12">
+        <f>B5/C5</f>
+        <v/>
+      </c>
+      <c r="M5" s="12">
+        <f>(B5-H5)/C5</f>
+        <v/>
+      </c>
+      <c r="N5" s="13">
         <f>RANK(F5,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M5" s="12">
+      <c r="O5" s="13">
         <f>RANK(K5,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <f>Raw_Data!A6</f>
         <v/>
       </c>
@@ -1356,7 +1423,7 @@
         <f>Raw_Data!B6</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <f>D6/E6</f>
         <v/>
       </c>
@@ -1376,15 +1443,23 @@
         <f>G6+H6-I6</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="15">
         <f>J6/E6</f>
         <v/>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="16">
+        <f>B6/C6</f>
+        <v/>
+      </c>
+      <c r="M6" s="16">
+        <f>(B6-H6)/C6</f>
+        <v/>
+      </c>
+      <c r="N6" s="17">
         <f>RANK(F6,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M6" s="15">
+      <c r="O6" s="17">
         <f>RANK(K6,$K$3:$K$12,1)</f>
         <v/>
       </c>
@@ -1435,16 +1510,24 @@
         <v/>
       </c>
       <c r="L7" s="12">
+        <f>B7/C7</f>
+        <v/>
+      </c>
+      <c r="M7" s="12">
+        <f>(B7-H7)/C7</f>
+        <v/>
+      </c>
+      <c r="N7" s="13">
         <f>RANK(F7,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M7" s="12">
+      <c r="O7" s="13">
         <f>RANK(K7,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>Raw_Data!A8</f>
         <v/>
       </c>
@@ -1464,7 +1547,7 @@
         <f>Raw_Data!B8</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <f>D8/E8</f>
         <v/>
       </c>
@@ -1484,15 +1567,23 @@
         <f>G8+H8-I8</f>
         <v/>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="15">
         <f>J8/E8</f>
         <v/>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="16">
+        <f>B8/C8</f>
+        <v/>
+      </c>
+      <c r="M8" s="16">
+        <f>(B8-H8)/C8</f>
+        <v/>
+      </c>
+      <c r="N8" s="17">
         <f>RANK(F8,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M8" s="15">
+      <c r="O8" s="17">
         <f>RANK(K8,$K$3:$K$12,1)</f>
         <v/>
       </c>
@@ -1543,16 +1634,24 @@
         <v/>
       </c>
       <c r="L9" s="12">
+        <f>B9/C9</f>
+        <v/>
+      </c>
+      <c r="M9" s="12">
+        <f>(B9-H9)/C9</f>
+        <v/>
+      </c>
+      <c r="N9" s="13">
         <f>RANK(F9,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M9" s="12">
+      <c r="O9" s="13">
         <f>RANK(K9,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>Raw_Data!A10</f>
         <v/>
       </c>
@@ -1572,7 +1671,7 @@
         <f>Raw_Data!B10</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <f>D10/E10</f>
         <v/>
       </c>
@@ -1592,15 +1691,23 @@
         <f>G10+H10-I10</f>
         <v/>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="15">
         <f>J10/E10</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="16">
+        <f>B10/C10</f>
+        <v/>
+      </c>
+      <c r="M10" s="16">
+        <f>(B10-H10)/C10</f>
+        <v/>
+      </c>
+      <c r="N10" s="17">
         <f>RANK(F10,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M10" s="15">
+      <c r="O10" s="17">
         <f>RANK(K10,$K$3:$K$12,1)</f>
         <v/>
       </c>
@@ -1651,16 +1758,24 @@
         <v/>
       </c>
       <c r="L11" s="12">
+        <f>B11/C11</f>
+        <v/>
+      </c>
+      <c r="M11" s="12">
+        <f>(B11-H11)/C11</f>
+        <v/>
+      </c>
+      <c r="N11" s="13">
         <f>RANK(F11,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M11" s="12">
+      <c r="O11" s="13">
         <f>RANK(K11,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>Raw_Data!A12</f>
         <v/>
       </c>
@@ -1680,7 +1795,7 @@
         <f>Raw_Data!B12</f>
         <v/>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="15">
         <f>D12/E12</f>
         <v/>
       </c>
@@ -1700,54 +1815,86 @@
         <f>G12+H12-I12</f>
         <v/>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="15">
         <f>J12/E12</f>
         <v/>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="16">
+        <f>B12/C12</f>
+        <v/>
+      </c>
+      <c r="M12" s="16">
+        <f>(B12-H12)/C12</f>
+        <v/>
+      </c>
+      <c r="N12" s="17">
         <f>RANK(F12,$F$3:$F$12,1)</f>
         <v/>
       </c>
-      <c r="M12" s="15">
+      <c r="O12" s="17">
         <f>RANK(K12,$K$3:$K$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Best-in-Class WC/Rev  → </t>
-        </is>
-      </c>
-      <c r="F14" s="17">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Best-in-Class WC/Rev  →</t>
+        </is>
+      </c>
+      <c r="F14" s="19">
         <f>MIN(F3:F12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Best-in-Class NWC/Rev →</t>
         </is>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="19">
         <f>MIN(K3:K12)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Best-in-Class = Lowest WC/Revenue &amp; NWC/Revenue (less capital tied up per $ of revenue). WC includes cash (financing decision). Operational NWC = AR + Inventory – AP (operations only).</t>
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Peer-Avg Current Ratio →</t>
+        </is>
+      </c>
+      <c r="L16" s="20">
+        <f>AVERAGE(L3:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Peer-Avg Quick Ratio   →</t>
+        </is>
+      </c>
+      <c r="M17" s="20">
+        <f>AVERAGE(M3:M12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Current Ratio=TCA÷TCL | Quick Ratio=(TCA–Inv)÷TCL | Operational NWC=AR+Inv–AP (excludes cash/short-term debt).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A19:O19"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1759,30 +1906,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Efficiency Metrics: DSO | DIO | DPO | CCC | AR Turns | Cash Return Ratio — All formulas reference Raw_Data</t>
+          <t>Efficiency Metrics: DSO | AR Turns | DIO | Inv Turns | DPO | CCC | CRR — All formulas reference Raw_Data</t>
         </is>
       </c>
     </row>
@@ -1806,8 +1956,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Accounts
-Receivable ($M)</t>
+          <t>AR
+($M)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1818,8 +1968,8 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Accounts
-Payable ($M)</t>
+          <t>AP
+($M)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1832,56 +1982,72 @@
         <is>
           <t>DSO (days)
 [=AR÷Rev×365]
-(lower=better)</t>
+(↓ better)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>AR Turns
 [=Rev÷AR]
-(higher=better)</t>
+(↑ better)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>DIO (days)
 [=Inv÷COGS×365]
-(lower=better)</t>
+(↓ better)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Inv Turns
+[=COGS÷Inv]
+(↑ better)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>DPO (days)
 [=AP÷COGS×365]
-(higher=better)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+(↑ better)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>CCC (days)
 [=DSO+DIO–DPO]
-(lower=better)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Cash Return
-Ratio
+(↓ better)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>CRR
 [=OCF÷Rev]
-(higher=better)</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>DSO
-Rank
+(↑ better)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>DSO Rank
 (1=Best)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>CRR
-Rank
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>DIO Rank
+(1=Best)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>DPO Rank
+(1=Best)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>CCC Rank
 (1=Best)</t>
         </is>
       </c>
@@ -1915,41 +2081,53 @@
         <f>Raw_Data!J3</f>
         <v/>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="21">
         <f>D3/B3*365</f>
         <v/>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="21">
         <f>B3/D3</f>
         <v/>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="21">
         <f>E3/C3*365</f>
         <v/>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="21">
+        <f>C3/E3</f>
+        <v/>
+      </c>
+      <c r="L3" s="21">
         <f>F3/C3*365</f>
         <v/>
       </c>
-      <c r="L3" s="18">
-        <f>H3+J3-K3</f>
-        <v/>
-      </c>
-      <c r="M3" s="11">
+      <c r="M3" s="21">
+        <f>H3+J3-L3</f>
+        <v/>
+      </c>
+      <c r="N3" s="11">
         <f>G3/B3</f>
         <v/>
       </c>
-      <c r="N3" s="12">
+      <c r="O3" s="13">
         <f>RANK(H3,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O3" s="12">
-        <f>RANK(M3,$M$3:$M$12,0)</f>
+      <c r="P3" s="13">
+        <f>RANK(J3,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q3" s="13">
+        <f>RANK(L3,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R3" s="13">
+        <f>RANK(M3,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <f>Raw_Data!A4</f>
         <v/>
       </c>
@@ -1977,36 +2155,48 @@
         <f>Raw_Data!J4</f>
         <v/>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="22">
         <f>D4/B4*365</f>
         <v/>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="22">
         <f>B4/D4</f>
         <v/>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="22">
         <f>E4/C4*365</f>
         <v/>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="22">
+        <f>C4/E4</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
         <f>F4/C4*365</f>
         <v/>
       </c>
-      <c r="L4" s="19">
-        <f>H4+J4-K4</f>
-        <v/>
-      </c>
-      <c r="M4" s="14">
+      <c r="M4" s="22">
+        <f>H4+J4-L4</f>
+        <v/>
+      </c>
+      <c r="N4" s="15">
         <f>G4/B4</f>
         <v/>
       </c>
-      <c r="N4" s="15">
+      <c r="O4" s="17">
         <f>RANK(H4,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O4" s="15">
-        <f>RANK(M4,$M$3:$M$12,0)</f>
+      <c r="P4" s="17">
+        <f>RANK(J4,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="17">
+        <f>RANK(L4,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R4" s="17">
+        <f>RANK(M4,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
@@ -2039,41 +2229,53 @@
         <f>Raw_Data!J5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="21">
         <f>D5/B5*365</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="21">
         <f>B5/D5</f>
         <v/>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="21">
         <f>E5/C5*365</f>
         <v/>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="21">
+        <f>C5/E5</f>
+        <v/>
+      </c>
+      <c r="L5" s="21">
         <f>F5/C5*365</f>
         <v/>
       </c>
-      <c r="L5" s="18">
-        <f>H5+J5-K5</f>
-        <v/>
-      </c>
-      <c r="M5" s="11">
+      <c r="M5" s="21">
+        <f>H5+J5-L5</f>
+        <v/>
+      </c>
+      <c r="N5" s="11">
         <f>G5/B5</f>
         <v/>
       </c>
-      <c r="N5" s="12">
+      <c r="O5" s="13">
         <f>RANK(H5,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O5" s="12">
-        <f>RANK(M5,$M$3:$M$12,0)</f>
+      <c r="P5" s="13">
+        <f>RANK(J5,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="13">
+        <f>RANK(L5,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R5" s="13">
+        <f>RANK(M5,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <f>Raw_Data!A6</f>
         <v/>
       </c>
@@ -2101,36 +2303,48 @@
         <f>Raw_Data!J6</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="22">
         <f>D6/B6*365</f>
         <v/>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="22">
         <f>B6/D6</f>
         <v/>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="22">
         <f>E6/C6*365</f>
         <v/>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="22">
+        <f>C6/E6</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
         <f>F6/C6*365</f>
         <v/>
       </c>
-      <c r="L6" s="19">
-        <f>H6+J6-K6</f>
-        <v/>
-      </c>
-      <c r="M6" s="14">
+      <c r="M6" s="22">
+        <f>H6+J6-L6</f>
+        <v/>
+      </c>
+      <c r="N6" s="15">
         <f>G6/B6</f>
         <v/>
       </c>
-      <c r="N6" s="15">
+      <c r="O6" s="17">
         <f>RANK(H6,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O6" s="15">
-        <f>RANK(M6,$M$3:$M$12,0)</f>
+      <c r="P6" s="17">
+        <f>RANK(J6,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="17">
+        <f>RANK(L6,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R6" s="17">
+        <f>RANK(M6,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
@@ -2163,41 +2377,53 @@
         <f>Raw_Data!J7</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="21">
         <f>D7/B7*365</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="21">
         <f>B7/D7</f>
         <v/>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="21">
         <f>E7/C7*365</f>
         <v/>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="21">
+        <f>C7/E7</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
         <f>F7/C7*365</f>
         <v/>
       </c>
-      <c r="L7" s="18">
-        <f>H7+J7-K7</f>
-        <v/>
-      </c>
-      <c r="M7" s="11">
+      <c r="M7" s="21">
+        <f>H7+J7-L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="11">
         <f>G7/B7</f>
         <v/>
       </c>
-      <c r="N7" s="12">
+      <c r="O7" s="13">
         <f>RANK(H7,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O7" s="12">
-        <f>RANK(M7,$M$3:$M$12,0)</f>
+      <c r="P7" s="13">
+        <f>RANK(J7,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="13">
+        <f>RANK(L7,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R7" s="13">
+        <f>RANK(M7,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>Raw_Data!A8</f>
         <v/>
       </c>
@@ -2225,36 +2451,48 @@
         <f>Raw_Data!J8</f>
         <v/>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="22">
         <f>D8/B8*365</f>
         <v/>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="22">
         <f>B8/D8</f>
         <v/>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="22">
         <f>E8/C8*365</f>
         <v/>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="22">
+        <f>C8/E8</f>
+        <v/>
+      </c>
+      <c r="L8" s="22">
         <f>F8/C8*365</f>
         <v/>
       </c>
-      <c r="L8" s="19">
-        <f>H8+J8-K8</f>
-        <v/>
-      </c>
-      <c r="M8" s="14">
+      <c r="M8" s="22">
+        <f>H8+J8-L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="15">
         <f>G8/B8</f>
         <v/>
       </c>
-      <c r="N8" s="15">
+      <c r="O8" s="17">
         <f>RANK(H8,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O8" s="15">
-        <f>RANK(M8,$M$3:$M$12,0)</f>
+      <c r="P8" s="17">
+        <f>RANK(J8,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="17">
+        <f>RANK(L8,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R8" s="17">
+        <f>RANK(M8,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
@@ -2287,41 +2525,53 @@
         <f>Raw_Data!J9</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="21">
         <f>D9/B9*365</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="21">
         <f>B9/D9</f>
         <v/>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="21">
         <f>E9/C9*365</f>
         <v/>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="21">
+        <f>C9/E9</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
         <f>F9/C9*365</f>
         <v/>
       </c>
-      <c r="L9" s="18">
-        <f>H9+J9-K9</f>
-        <v/>
-      </c>
-      <c r="M9" s="11">
+      <c r="M9" s="21">
+        <f>H9+J9-L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="11">
         <f>G9/B9</f>
         <v/>
       </c>
-      <c r="N9" s="12">
+      <c r="O9" s="13">
         <f>RANK(H9,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O9" s="12">
-        <f>RANK(M9,$M$3:$M$12,0)</f>
+      <c r="P9" s="13">
+        <f>RANK(J9,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="13">
+        <f>RANK(L9,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R9" s="13">
+        <f>RANK(M9,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>Raw_Data!A10</f>
         <v/>
       </c>
@@ -2349,36 +2599,48 @@
         <f>Raw_Data!J10</f>
         <v/>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="22">
         <f>D10/B10*365</f>
         <v/>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="22">
         <f>B10/D10</f>
         <v/>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="22">
         <f>E10/C10*365</f>
         <v/>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="22">
+        <f>C10/E10</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
         <f>F10/C10*365</f>
         <v/>
       </c>
-      <c r="L10" s="19">
-        <f>H10+J10-K10</f>
-        <v/>
-      </c>
-      <c r="M10" s="14">
+      <c r="M10" s="22">
+        <f>H10+J10-L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="15">
         <f>G10/B10</f>
         <v/>
       </c>
-      <c r="N10" s="15">
+      <c r="O10" s="17">
         <f>RANK(H10,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O10" s="15">
-        <f>RANK(M10,$M$3:$M$12,0)</f>
+      <c r="P10" s="17">
+        <f>RANK(J10,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="17">
+        <f>RANK(L10,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R10" s="17">
+        <f>RANK(M10,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
@@ -2411,41 +2673,53 @@
         <f>Raw_Data!J11</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="21">
         <f>D11/B11*365</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="21">
         <f>B11/D11</f>
         <v/>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="21">
         <f>E11/C11*365</f>
         <v/>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="21">
+        <f>C11/E11</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
         <f>F11/C11*365</f>
         <v/>
       </c>
-      <c r="L11" s="18">
-        <f>H11+J11-K11</f>
-        <v/>
-      </c>
-      <c r="M11" s="11">
+      <c r="M11" s="21">
+        <f>H11+J11-L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="11">
         <f>G11/B11</f>
         <v/>
       </c>
-      <c r="N11" s="12">
+      <c r="O11" s="13">
         <f>RANK(H11,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O11" s="12">
-        <f>RANK(M11,$M$3:$M$12,0)</f>
+      <c r="P11" s="13">
+        <f>RANK(J11,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="13">
+        <f>RANK(L11,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R11" s="13">
+        <f>RANK(M11,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>Raw_Data!A12</f>
         <v/>
       </c>
@@ -2473,122 +2747,146 @@
         <f>Raw_Data!J12</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="22">
         <f>D12/B12*365</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="22">
         <f>B12/D12</f>
         <v/>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="22">
         <f>E12/C12*365</f>
         <v/>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="22">
+        <f>C12/E12</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
         <f>F12/C12*365</f>
         <v/>
       </c>
-      <c r="L12" s="19">
-        <f>H12+J12-K12</f>
-        <v/>
-      </c>
-      <c r="M12" s="14">
+      <c r="M12" s="22">
+        <f>H12+J12-L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="15">
         <f>G12/B12</f>
         <v/>
       </c>
-      <c r="N12" s="15">
+      <c r="O12" s="17">
         <f>RANK(H12,$H$3:$H$12,1)</f>
         <v/>
       </c>
-      <c r="O12" s="15">
-        <f>RANK(M12,$M$3:$M$12,0)</f>
+      <c r="P12" s="17">
+        <f>RANK(J12,$J$3:$J$12,1)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="17">
+        <f>RANK(L12,$L$3:$L$12,0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="17">
+        <f>RANK(M12,$M$3:$M$12,1)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Best DSO (Min):</t>
         </is>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="23">
         <f>MIN(H3:H12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Best AR Turns (Max):</t>
         </is>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="23">
         <f>MAX(I3:I12)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Best DIO (Min):</t>
         </is>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="23">
         <f>MIN(J3:J12)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Best Inv Turns (Max):</t>
+        </is>
+      </c>
+      <c r="K17" s="23">
+        <f>MAX(K3:K12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Best DPO (Max):</t>
         </is>
       </c>
-      <c r="K17" s="20">
-        <f>MAX(K3:K12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="L18" s="23">
+        <f>MAX(L3:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Best CCC (Min):</t>
         </is>
       </c>
-      <c r="L18" s="20">
-        <f>MIN(L3:L12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="M19" s="23">
+        <f>MIN(M3:M12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Best CRR (Max):</t>
         </is>
       </c>
-      <c r="M19" s="17">
-        <f>MAX(M3:M12)</f>
+      <c r="N20" s="19">
+        <f>MAX(N3:N12)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>DSO=Days Sales Outstanding | DIO=Days Inventory Outstanding | DPO=Days Payables Outstanding | CCC=Cash Conversion Cycle | AR Turns=Annualised receivable cycles | CRR=Cash Return Ratio. All computed from Raw_Data. Fiscal year timing differences exist (see Raw_Data notes).</t>
+          <t>DPO Rank: higher DPO = better (supplier financing). CCC Rank: lower CCC = better. Inv Turns = COGS÷Inventory. AR Turns = Revenue÷AR. CRR = OCF÷Revenue.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A21:R21"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A21:O21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2600,27 +2898,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Overall Scoring Model — Rank-Sum Method (4 Equal-Weight Metrics | Lower Total Score = Better Overall)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="50" customHeight="1">
+          <t>Overall Scoring Model — Rank-Sum (6 Metrics | Equal Weight | Lower Total Score = Better Overall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Company</t>
@@ -2628,47 +2928,54 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>WC/Rev
-Rank
-[from WC_NWC!L]</t>
+          <t>WC/Rev Rank
+[WC_NWC!N]</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NWC/Rev
-Rank
-[from WC_NWC!M]</t>
+          <t>NWC/Rev Rank
+[WC_NWC!O]</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>DSO
-Rank
-[from Efficiency!N]</t>
+          <t>DSO Rank
+[Eff!P]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>CRR
-Rank
-[from Efficiency!O]</t>
+          <t>DIO Rank
+[Eff!Q]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>DPO Rank
+[Eff!R]</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>CCC Rank
+[Eff!S]</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>Total Score
-[=SUM(B:E)]
-Lower = Better</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Overall
-Rank
-[=RANK(...)]</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+[=SUM(B:G)]
+Lower=Better</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Overall Rank
+[=RANK(…)]</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Quartile
 [=IF(rank≤2,Q1,…)]</t>
@@ -2680,66 +2987,82 @@
         <f>Raw_Data!A3</f>
         <v/>
       </c>
-      <c r="B3" s="12">
-        <f>WC_NWC!L3</f>
-        <v/>
-      </c>
-      <c r="C3" s="12">
-        <f>WC_NWC!M3</f>
-        <v/>
-      </c>
-      <c r="D3" s="12">
-        <f>Efficiency_Metrics!N3</f>
-        <v/>
-      </c>
-      <c r="E3" s="12">
-        <f>Efficiency_Metrics!O3</f>
-        <v/>
-      </c>
-      <c r="F3" s="12">
-        <f>SUM(B3:E3)</f>
-        <v/>
-      </c>
-      <c r="G3" s="12">
-        <f>RANK(F3,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H3" s="5">
-        <f>IF(G3&lt;=2,"Q1",IF(G3&lt;=5,"Q2",IF(G3&lt;=7,"Q3","Q4")))</f>
+      <c r="B3" s="13">
+        <f>WC_NWC!N3</f>
+        <v/>
+      </c>
+      <c r="C3" s="13">
+        <f>WC_NWC!O3</f>
+        <v/>
+      </c>
+      <c r="D3" s="13">
+        <f>Efficiency_Metrics!P3</f>
+        <v/>
+      </c>
+      <c r="E3" s="13">
+        <f>Efficiency_Metrics!Q3</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>Efficiency_Metrics!R3</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>Efficiency_Metrics!S3</f>
+        <v/>
+      </c>
+      <c r="H3" s="13">
+        <f>SUM(B3:G3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="13">
+        <f>RANK(H3,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J3" s="5">
+        <f>IF(I3&lt;=2,"Q1",IF(I3&lt;=5,"Q2",IF(I3&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <f>Raw_Data!A4</f>
         <v/>
       </c>
-      <c r="B4" s="15">
-        <f>WC_NWC!L4</f>
-        <v/>
-      </c>
-      <c r="C4" s="15">
-        <f>WC_NWC!M4</f>
-        <v/>
-      </c>
-      <c r="D4" s="15">
-        <f>Efficiency_Metrics!N4</f>
-        <v/>
-      </c>
-      <c r="E4" s="15">
-        <f>Efficiency_Metrics!O4</f>
-        <v/>
-      </c>
-      <c r="F4" s="15">
-        <f>SUM(B4:E4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="15">
-        <f>RANK(F4,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H4" s="8">
-        <f>IF(G4&lt;=2,"Q1",IF(G4&lt;=5,"Q2",IF(G4&lt;=7,"Q3","Q4")))</f>
+      <c r="B4" s="17">
+        <f>WC_NWC!N4</f>
+        <v/>
+      </c>
+      <c r="C4" s="17">
+        <f>WC_NWC!O4</f>
+        <v/>
+      </c>
+      <c r="D4" s="17">
+        <f>Efficiency_Metrics!P4</f>
+        <v/>
+      </c>
+      <c r="E4" s="17">
+        <f>Efficiency_Metrics!Q4</f>
+        <v/>
+      </c>
+      <c r="F4" s="17">
+        <f>Efficiency_Metrics!R4</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
+        <f>Efficiency_Metrics!S4</f>
+        <v/>
+      </c>
+      <c r="H4" s="17">
+        <f>SUM(B4:G4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="17">
+        <f>RANK(H4,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IF(I4&lt;=2,"Q1",IF(I4&lt;=5,"Q2",IF(I4&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
@@ -2748,66 +3071,82 @@
         <f>Raw_Data!A5</f>
         <v/>
       </c>
-      <c r="B5" s="12">
-        <f>WC_NWC!L5</f>
-        <v/>
-      </c>
-      <c r="C5" s="12">
-        <f>WC_NWC!M5</f>
-        <v/>
-      </c>
-      <c r="D5" s="12">
-        <f>Efficiency_Metrics!N5</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
-        <f>Efficiency_Metrics!O5</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>SUM(B5:E5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12">
-        <f>RANK(F5,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H5" s="5">
-        <f>IF(G5&lt;=2,"Q1",IF(G5&lt;=5,"Q2",IF(G5&lt;=7,"Q3","Q4")))</f>
+      <c r="B5" s="13">
+        <f>WC_NWC!N5</f>
+        <v/>
+      </c>
+      <c r="C5" s="13">
+        <f>WC_NWC!O5</f>
+        <v/>
+      </c>
+      <c r="D5" s="13">
+        <f>Efficiency_Metrics!P5</f>
+        <v/>
+      </c>
+      <c r="E5" s="13">
+        <f>Efficiency_Metrics!Q5</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>Efficiency_Metrics!R5</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>Efficiency_Metrics!S5</f>
+        <v/>
+      </c>
+      <c r="H5" s="13">
+        <f>SUM(B5:G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="13">
+        <f>RANK(H5,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>IF(I5&lt;=2,"Q1",IF(I5&lt;=5,"Q2",IF(I5&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <f>Raw_Data!A6</f>
         <v/>
       </c>
-      <c r="B6" s="15">
-        <f>WC_NWC!L6</f>
-        <v/>
-      </c>
-      <c r="C6" s="15">
-        <f>WC_NWC!M6</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>Efficiency_Metrics!N6</f>
-        <v/>
-      </c>
-      <c r="E6" s="15">
-        <f>Efficiency_Metrics!O6</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>SUM(B6:E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="15">
-        <f>RANK(F6,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H6" s="8">
-        <f>IF(G6&lt;=2,"Q1",IF(G6&lt;=5,"Q2",IF(G6&lt;=7,"Q3","Q4")))</f>
+      <c r="B6" s="17">
+        <f>WC_NWC!N6</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
+        <f>WC_NWC!O6</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>Efficiency_Metrics!P6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Efficiency_Metrics!Q6</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>Efficiency_Metrics!R6</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>Efficiency_Metrics!S6</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>SUM(B6:G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>RANK(H6,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>IF(I6&lt;=2,"Q1",IF(I6&lt;=5,"Q2",IF(I6&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
@@ -2816,66 +3155,82 @@
         <f>Raw_Data!A7</f>
         <v/>
       </c>
-      <c r="B7" s="12">
-        <f>WC_NWC!L7</f>
-        <v/>
-      </c>
-      <c r="C7" s="12">
-        <f>WC_NWC!M7</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
-        <f>Efficiency_Metrics!N7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
-        <f>Efficiency_Metrics!O7</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>SUM(B7:E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12">
-        <f>RANK(F7,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H7" s="5">
-        <f>IF(G7&lt;=2,"Q1",IF(G7&lt;=5,"Q2",IF(G7&lt;=7,"Q3","Q4")))</f>
+      <c r="B7" s="13">
+        <f>WC_NWC!N7</f>
+        <v/>
+      </c>
+      <c r="C7" s="13">
+        <f>WC_NWC!O7</f>
+        <v/>
+      </c>
+      <c r="D7" s="13">
+        <f>Efficiency_Metrics!P7</f>
+        <v/>
+      </c>
+      <c r="E7" s="13">
+        <f>Efficiency_Metrics!Q7</f>
+        <v/>
+      </c>
+      <c r="F7" s="13">
+        <f>Efficiency_Metrics!R7</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>Efficiency_Metrics!S7</f>
+        <v/>
+      </c>
+      <c r="H7" s="13">
+        <f>SUM(B7:G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="13">
+        <f>RANK(H7,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(I7&lt;=2,"Q1",IF(I7&lt;=5,"Q2",IF(I7&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>Raw_Data!A8</f>
         <v/>
       </c>
-      <c r="B8" s="15">
-        <f>WC_NWC!L8</f>
-        <v/>
-      </c>
-      <c r="C8" s="15">
-        <f>WC_NWC!M8</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>Efficiency_Metrics!N8</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>Efficiency_Metrics!O8</f>
-        <v/>
-      </c>
-      <c r="F8" s="15">
-        <f>SUM(B8:E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="15">
-        <f>RANK(F8,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H8" s="8">
-        <f>IF(G8&lt;=2,"Q1",IF(G8&lt;=5,"Q2",IF(G8&lt;=7,"Q3","Q4")))</f>
+      <c r="B8" s="17">
+        <f>WC_NWC!N8</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>WC_NWC!O8</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>Efficiency_Metrics!P8</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>Efficiency_Metrics!Q8</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>Efficiency_Metrics!R8</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>Efficiency_Metrics!S8</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>SUM(B8:G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>RANK(H8,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J8" s="8">
+        <f>IF(I8&lt;=2,"Q1",IF(I8&lt;=5,"Q2",IF(I8&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
@@ -2884,66 +3239,82 @@
         <f>Raw_Data!A9</f>
         <v/>
       </c>
-      <c r="B9" s="12">
-        <f>WC_NWC!L9</f>
-        <v/>
-      </c>
-      <c r="C9" s="12">
-        <f>WC_NWC!M9</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>Efficiency_Metrics!N9</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
-        <f>Efficiency_Metrics!O9</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>SUM(B9:E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12">
-        <f>RANK(F9,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(G9&lt;=2,"Q1",IF(G9&lt;=5,"Q2",IF(G9&lt;=7,"Q3","Q4")))</f>
+      <c r="B9" s="13">
+        <f>WC_NWC!N9</f>
+        <v/>
+      </c>
+      <c r="C9" s="13">
+        <f>WC_NWC!O9</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>Efficiency_Metrics!P9</f>
+        <v/>
+      </c>
+      <c r="E9" s="13">
+        <f>Efficiency_Metrics!Q9</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>Efficiency_Metrics!R9</f>
+        <v/>
+      </c>
+      <c r="G9" s="13">
+        <f>Efficiency_Metrics!S9</f>
+        <v/>
+      </c>
+      <c r="H9" s="13">
+        <f>SUM(B9:G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="13">
+        <f>RANK(H9,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>IF(I9&lt;=2,"Q1",IF(I9&lt;=5,"Q2",IF(I9&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>Raw_Data!A10</f>
         <v/>
       </c>
-      <c r="B10" s="15">
-        <f>WC_NWC!L10</f>
-        <v/>
-      </c>
-      <c r="C10" s="15">
-        <f>WC_NWC!M10</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>Efficiency_Metrics!N10</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>Efficiency_Metrics!O10</f>
-        <v/>
-      </c>
-      <c r="F10" s="15">
-        <f>SUM(B10:E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="15">
-        <f>RANK(F10,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>IF(G10&lt;=2,"Q1",IF(G10&lt;=5,"Q2",IF(G10&lt;=7,"Q3","Q4")))</f>
+      <c r="B10" s="17">
+        <f>WC_NWC!N10</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>WC_NWC!O10</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>Efficiency_Metrics!P10</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>Efficiency_Metrics!Q10</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>Efficiency_Metrics!R10</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>Efficiency_Metrics!S10</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>SUM(B10:G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>RANK(H10,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J10" s="8">
+        <f>IF(I10&lt;=2,"Q1",IF(I10&lt;=5,"Q2",IF(I10&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
@@ -2952,80 +3323,96 @@
         <f>Raw_Data!A11</f>
         <v/>
       </c>
-      <c r="B11" s="12">
-        <f>WC_NWC!L11</f>
-        <v/>
-      </c>
-      <c r="C11" s="12">
-        <f>WC_NWC!M11</f>
-        <v/>
-      </c>
-      <c r="D11" s="12">
-        <f>Efficiency_Metrics!N11</f>
-        <v/>
-      </c>
-      <c r="E11" s="12">
-        <f>Efficiency_Metrics!O11</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>SUM(B11:E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12">
-        <f>RANK(F11,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H11" s="5">
-        <f>IF(G11&lt;=2,"Q1",IF(G11&lt;=5,"Q2",IF(G11&lt;=7,"Q3","Q4")))</f>
+      <c r="B11" s="13">
+        <f>WC_NWC!N11</f>
+        <v/>
+      </c>
+      <c r="C11" s="13">
+        <f>WC_NWC!O11</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>Efficiency_Metrics!P11</f>
+        <v/>
+      </c>
+      <c r="E11" s="13">
+        <f>Efficiency_Metrics!Q11</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>Efficiency_Metrics!R11</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>Efficiency_Metrics!S11</f>
+        <v/>
+      </c>
+      <c r="H11" s="13">
+        <f>SUM(B11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="13">
+        <f>RANK(H11,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J11" s="5">
+        <f>IF(I11&lt;=2,"Q1",IF(I11&lt;=5,"Q2",IF(I11&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>Raw_Data!A12</f>
         <v/>
       </c>
-      <c r="B12" s="15">
-        <f>WC_NWC!L12</f>
-        <v/>
-      </c>
-      <c r="C12" s="15">
-        <f>WC_NWC!M12</f>
-        <v/>
-      </c>
-      <c r="D12" s="15">
-        <f>Efficiency_Metrics!N12</f>
-        <v/>
-      </c>
-      <c r="E12" s="15">
-        <f>Efficiency_Metrics!O12</f>
-        <v/>
-      </c>
-      <c r="F12" s="15">
-        <f>SUM(B12:E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="15">
-        <f>RANK(F12,$F$3:$F$12,1)</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>IF(G12&lt;=2,"Q1",IF(G12&lt;=5,"Q2",IF(G12&lt;=7,"Q3","Q4")))</f>
+      <c r="B12" s="17">
+        <f>WC_NWC!N12</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>WC_NWC!O12</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>Efficiency_Metrics!P12</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>Efficiency_Metrics!Q12</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>Efficiency_Metrics!R12</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>Efficiency_Metrics!S12</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>SUM(B12:G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>RANK(H12,$H$3:$H$12,1)</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>IF(I12&lt;=2,"Q1",IF(I12&lt;=5,"Q2",IF(I12&lt;=7,"Q3","Q4")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>AR Turns excluded from scoring (mathematically inverse of DSO → would double-count). 4 metrics: WC/Rev, NWC/Rev, DSO, CRR — equal weight. Quartile: Q1=Rank 1-2 (top 20%) | Q2=Rank 3-5 | Q3=Rank 6-7 | Q4=Rank 8-10.</t>
+          <t>AR Turns &amp; Inv Turns excluded (inverse of DSO/DIO → would double-count). 6 metrics: WC/Rev, NWC/Rev, DSO, DIO, DPO, CCC — equal weight. DPO rank flipped so higher DPO = rank 1 (benefit).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3037,27 +3424,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gap-to-Best-Practice Benchmark Analysis — All gaps computed dynamically via formulas</t>
+          <t>Gap-to-Best-Practice Benchmark Analysis — DSO | DIO | DPO | CCC | NWC/Rev | CRR</t>
         </is>
       </c>
     </row>
@@ -3086,56 +3479,91 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Best-Practice
-DSO (days)
-[=MIN(...)]</t>
+          <t>Best DSO
+[=MIN]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>DSO Gap
-(days)
-[=Actual–Best]
-+ve = worse</t>
+[Act–Best]
++ve=worse</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>DIO
+(days)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Best DIO
+[=MIN]</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>DIO Gap
+[Act–Best]
++ve=worse</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>DPO
+(days)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Best DPO
+[=MAX]</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>DPO Gap
+[Best–Act]
++ve=worse</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>CCC
+(days)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Best CCC
+[=MIN]</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>CCC Gap
+[Act–Best]
++ve=worse</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>NWC/Rev
 (%)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Best-Practice
-NWC/Rev
-[=MIN(...)]</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>NWC Gap (pp)
-[=Actual–Best]
-+ve = worse</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>CRR (%)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Best-Practice
-CRR
-[=MAX(...)]</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>CRR Gap (pp)
-[=Best–Actual]
-+ve = worse</t>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Best NWC/Rev
+[=MIN]</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>NWC Gap
+[Act–Best]
++ve=worse</t>
         </is>
       </c>
     </row>
@@ -3144,98 +3572,146 @@
         <f>Raw_Data!A3</f>
         <v/>
       </c>
-      <c r="B3" s="12">
-        <f>Scoring_Ranking!G3</f>
+      <c r="B3" s="13">
+        <f>Scoring_Ranking!I3</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Scoring_Ranking!H3</f>
-        <v/>
-      </c>
-      <c r="D3" s="18">
+        <f>Scoring_Ranking!J3</f>
+        <v/>
+      </c>
+      <c r="D3" s="21">
         <f>Efficiency_Metrics!H3</f>
         <v/>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="21">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="21">
         <f>D3-E3</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="21">
+        <f>Efficiency_Metrics!J3</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v/>
+      </c>
+      <c r="J3" s="21">
+        <f>Efficiency_Metrics!L3</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L3" s="21">
+        <f>K3-J3</f>
+        <v/>
+      </c>
+      <c r="M3" s="21">
+        <f>Efficiency_Metrics!M3</f>
+        <v/>
+      </c>
+      <c r="N3" s="21">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O3" s="21">
+        <f>M3-N3</f>
+        <v/>
+      </c>
+      <c r="P3" s="11">
         <f>WC_NWC!K3</f>
         <v/>
       </c>
-      <c r="H3" s="11">
+      <c r="Q3" s="11">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I3" s="11">
-        <f>G3-H3</f>
-        <v/>
-      </c>
-      <c r="J3" s="11">
-        <f>Efficiency_Metrics!M3</f>
-        <v/>
-      </c>
-      <c r="K3" s="11">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L3" s="11">
-        <f>K3-J3</f>
+      <c r="R3" s="11">
+        <f>P3-Q3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <f>Raw_Data!A4</f>
         <v/>
       </c>
-      <c r="B4" s="15">
-        <f>Scoring_Ranking!G4</f>
+      <c r="B4" s="17">
+        <f>Scoring_Ranking!I4</f>
         <v/>
       </c>
       <c r="C4" s="8">
-        <f>Scoring_Ranking!H4</f>
-        <v/>
-      </c>
-      <c r="D4" s="19">
+        <f>Scoring_Ranking!J4</f>
+        <v/>
+      </c>
+      <c r="D4" s="22">
         <f>Efficiency_Metrics!H4</f>
         <v/>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="22">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="22">
         <f>D4-E4</f>
         <v/>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="22">
+        <f>Efficiency_Metrics!J4</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I4" s="22">
+        <f>G4-H4</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>Efficiency_Metrics!L4</f>
+        <v/>
+      </c>
+      <c r="K4" s="22">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>K4-J4</f>
+        <v/>
+      </c>
+      <c r="M4" s="22">
+        <f>Efficiency_Metrics!M4</f>
+        <v/>
+      </c>
+      <c r="N4" s="22">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O4" s="22">
+        <f>M4-N4</f>
+        <v/>
+      </c>
+      <c r="P4" s="15">
         <f>WC_NWC!K4</f>
         <v/>
       </c>
-      <c r="H4" s="14">
+      <c r="Q4" s="15">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I4" s="14">
-        <f>G4-H4</f>
-        <v/>
-      </c>
-      <c r="J4" s="14">
-        <f>Efficiency_Metrics!M4</f>
-        <v/>
-      </c>
-      <c r="K4" s="14">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L4" s="14">
-        <f>K4-J4</f>
+      <c r="R4" s="15">
+        <f>P4-Q4</f>
         <v/>
       </c>
     </row>
@@ -3244,98 +3720,146 @@
         <f>Raw_Data!A5</f>
         <v/>
       </c>
-      <c r="B5" s="12">
-        <f>Scoring_Ranking!G5</f>
+      <c r="B5" s="13">
+        <f>Scoring_Ranking!I5</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>Scoring_Ranking!H5</f>
-        <v/>
-      </c>
-      <c r="D5" s="18">
+        <f>Scoring_Ranking!J5</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
         <f>Efficiency_Metrics!H5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="21">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="21">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="21">
+        <f>Efficiency_Metrics!J5</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v/>
+      </c>
+      <c r="J5" s="21">
+        <f>Efficiency_Metrics!L5</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L5" s="21">
+        <f>K5-J5</f>
+        <v/>
+      </c>
+      <c r="M5" s="21">
+        <f>Efficiency_Metrics!M5</f>
+        <v/>
+      </c>
+      <c r="N5" s="21">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O5" s="21">
+        <f>M5-N5</f>
+        <v/>
+      </c>
+      <c r="P5" s="11">
         <f>WC_NWC!K5</f>
         <v/>
       </c>
-      <c r="H5" s="11">
+      <c r="Q5" s="11">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I5" s="11">
-        <f>G5-H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="11">
-        <f>Efficiency_Metrics!M5</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L5" s="11">
-        <f>K5-J5</f>
+      <c r="R5" s="11">
+        <f>P5-Q5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <f>Raw_Data!A6</f>
         <v/>
       </c>
-      <c r="B6" s="15">
-        <f>Scoring_Ranking!G6</f>
+      <c r="B6" s="17">
+        <f>Scoring_Ranking!I6</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>Scoring_Ranking!H6</f>
-        <v/>
-      </c>
-      <c r="D6" s="19">
+        <f>Scoring_Ranking!J6</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
         <f>Efficiency_Metrics!H6</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="22">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="22">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="22">
+        <f>Efficiency_Metrics!J6</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>G6-H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>Efficiency_Metrics!L6</f>
+        <v/>
+      </c>
+      <c r="K6" s="22">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
+        <f>K6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="22">
+        <f>Efficiency_Metrics!M6</f>
+        <v/>
+      </c>
+      <c r="N6" s="22">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O6" s="22">
+        <f>M6-N6</f>
+        <v/>
+      </c>
+      <c r="P6" s="15">
         <f>WC_NWC!K6</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="Q6" s="15">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I6" s="14">
-        <f>G6-H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="14">
-        <f>Efficiency_Metrics!M6</f>
-        <v/>
-      </c>
-      <c r="K6" s="14">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L6" s="14">
-        <f>K6-J6</f>
+      <c r="R6" s="15">
+        <f>P6-Q6</f>
         <v/>
       </c>
     </row>
@@ -3344,98 +3868,146 @@
         <f>Raw_Data!A7</f>
         <v/>
       </c>
-      <c r="B7" s="12">
-        <f>Scoring_Ranking!G7</f>
+      <c r="B7" s="13">
+        <f>Scoring_Ranking!I7</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>Scoring_Ranking!H7</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
+        <f>Scoring_Ranking!J7</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
         <f>Efficiency_Metrics!H7</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="21">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="21">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="21">
+        <f>Efficiency_Metrics!J7</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="21">
+        <f>Efficiency_Metrics!L7</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
+        <f>K7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
+        <f>Efficiency_Metrics!M7</f>
+        <v/>
+      </c>
+      <c r="N7" s="21">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O7" s="21">
+        <f>M7-N7</f>
+        <v/>
+      </c>
+      <c r="P7" s="11">
         <f>WC_NWC!K7</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="Q7" s="11">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I7" s="11">
-        <f>G7-H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="11">
-        <f>Efficiency_Metrics!M7</f>
-        <v/>
-      </c>
-      <c r="K7" s="11">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L7" s="11">
-        <f>K7-J7</f>
+      <c r="R7" s="11">
+        <f>P7-Q7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>Raw_Data!A8</f>
         <v/>
       </c>
-      <c r="B8" s="15">
-        <f>Scoring_Ranking!G8</f>
+      <c r="B8" s="17">
+        <f>Scoring_Ranking!I8</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>Scoring_Ranking!H8</f>
-        <v/>
-      </c>
-      <c r="D8" s="19">
+        <f>Scoring_Ranking!J8</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
         <f>Efficiency_Metrics!H8</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="22">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="22">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="22">
+        <f>Efficiency_Metrics!J8</f>
+        <v/>
+      </c>
+      <c r="H8" s="22">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>G8-H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>Efficiency_Metrics!L8</f>
+        <v/>
+      </c>
+      <c r="K8" s="22">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L8" s="22">
+        <f>K8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="22">
+        <f>Efficiency_Metrics!M8</f>
+        <v/>
+      </c>
+      <c r="N8" s="22">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O8" s="22">
+        <f>M8-N8</f>
+        <v/>
+      </c>
+      <c r="P8" s="15">
         <f>WC_NWC!K8</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="Q8" s="15">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I8" s="14">
-        <f>G8-H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="14">
-        <f>Efficiency_Metrics!M8</f>
-        <v/>
-      </c>
-      <c r="K8" s="14">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L8" s="14">
-        <f>K8-J8</f>
+      <c r="R8" s="15">
+        <f>P8-Q8</f>
         <v/>
       </c>
     </row>
@@ -3444,98 +4016,146 @@
         <f>Raw_Data!A9</f>
         <v/>
       </c>
-      <c r="B9" s="12">
-        <f>Scoring_Ranking!G9</f>
+      <c r="B9" s="13">
+        <f>Scoring_Ranking!I9</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>Scoring_Ranking!H9</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
+        <f>Scoring_Ranking!J9</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
         <f>Efficiency_Metrics!H9</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="21">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="21">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="21">
+        <f>Efficiency_Metrics!J9</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>Efficiency_Metrics!L9</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
+        <f>K9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="21">
+        <f>Efficiency_Metrics!M9</f>
+        <v/>
+      </c>
+      <c r="N9" s="21">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O9" s="21">
+        <f>M9-N9</f>
+        <v/>
+      </c>
+      <c r="P9" s="11">
         <f>WC_NWC!K9</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="Q9" s="11">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I9" s="11">
-        <f>G9-H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="11">
-        <f>Efficiency_Metrics!M9</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L9" s="11">
-        <f>K9-J9</f>
+      <c r="R9" s="11">
+        <f>P9-Q9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>Raw_Data!A10</f>
         <v/>
       </c>
-      <c r="B10" s="15">
-        <f>Scoring_Ranking!G10</f>
+      <c r="B10" s="17">
+        <f>Scoring_Ranking!I10</f>
         <v/>
       </c>
       <c r="C10" s="8">
-        <f>Scoring_Ranking!H10</f>
-        <v/>
-      </c>
-      <c r="D10" s="19">
+        <f>Scoring_Ranking!J10</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
         <f>Efficiency_Metrics!H10</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="22">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="22">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="22">
+        <f>Efficiency_Metrics!J10</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>G10-H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>Efficiency_Metrics!L10</f>
+        <v/>
+      </c>
+      <c r="K10" s="22">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
+        <f>K10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="22">
+        <f>Efficiency_Metrics!M10</f>
+        <v/>
+      </c>
+      <c r="N10" s="22">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O10" s="22">
+        <f>M10-N10</f>
+        <v/>
+      </c>
+      <c r="P10" s="15">
         <f>WC_NWC!K10</f>
         <v/>
       </c>
-      <c r="H10" s="14">
+      <c r="Q10" s="15">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I10" s="14">
-        <f>G10-H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="14">
-        <f>Efficiency_Metrics!M10</f>
-        <v/>
-      </c>
-      <c r="K10" s="14">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L10" s="14">
-        <f>K10-J10</f>
+      <c r="R10" s="15">
+        <f>P10-Q10</f>
         <v/>
       </c>
     </row>
@@ -3544,112 +4164,160 @@
         <f>Raw_Data!A11</f>
         <v/>
       </c>
-      <c r="B11" s="12">
-        <f>Scoring_Ranking!G11</f>
+      <c r="B11" s="13">
+        <f>Scoring_Ranking!I11</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>Scoring_Ranking!H11</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
+        <f>Scoring_Ranking!J11</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
         <f>Efficiency_Metrics!H11</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="21">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="21">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="21">
+        <f>Efficiency_Metrics!J11</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>Efficiency_Metrics!L11</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
+        <f>K11-J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
+        <f>Efficiency_Metrics!M11</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O11" s="21">
+        <f>M11-N11</f>
+        <v/>
+      </c>
+      <c r="P11" s="11">
         <f>WC_NWC!K11</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="Q11" s="11">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I11" s="11">
-        <f>G11-H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="11">
-        <f>Efficiency_Metrics!M11</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L11" s="11">
-        <f>K11-J11</f>
+      <c r="R11" s="11">
+        <f>P11-Q11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>Raw_Data!A12</f>
         <v/>
       </c>
-      <c r="B12" s="15">
-        <f>Scoring_Ranking!G12</f>
+      <c r="B12" s="17">
+        <f>Scoring_Ranking!I12</f>
         <v/>
       </c>
       <c r="C12" s="8">
-        <f>Scoring_Ranking!H12</f>
-        <v/>
-      </c>
-      <c r="D12" s="19">
+        <f>Scoring_Ranking!J12</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
         <f>Efficiency_Metrics!H12</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="22">
         <f>MIN(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="22">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="22">
+        <f>Efficiency_Metrics!J12</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>MIN(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>G12-H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>Efficiency_Metrics!L12</f>
+        <v/>
+      </c>
+      <c r="K12" s="22">
+        <f>MAX(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>K12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="22">
+        <f>Efficiency_Metrics!M12</f>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <f>MIN(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="22">
+        <f>M12-N12</f>
+        <v/>
+      </c>
+      <c r="P12" s="15">
         <f>WC_NWC!K12</f>
         <v/>
       </c>
-      <c r="H12" s="14">
+      <c r="Q12" s="15">
         <f>MIN(WC_NWC!$K$3:WC_NWC!$K$12)</f>
         <v/>
       </c>
-      <c r="I12" s="14">
-        <f>G12-H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="14">
-        <f>Efficiency_Metrics!M12</f>
-        <v/>
-      </c>
-      <c r="K12" s="14">
-        <f>MAX(Efficiency_Metrics!$M$3:Efficiency_Metrics!$M$12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="14">
-        <f>K12-J12</f>
+      <c r="R12" s="15">
+        <f>P12-Q12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Positive gap = company is WORSE than best practice. Best-practice DSO / NWC = MIN of peer group. Best-practice CRR = MAX of peer group. All best-practice values are dynamic — they update automatically if raw data changes.</t>
+          <t>DSO/DIO/CCC gap: positive = company is WORSE than best practice. DPO gap: positive = company is paying suppliers FASTER than best practice (cash disadvantage). All best-practice values are dynamic MIN/MAX across the peer group.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3661,31 +4329,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash Release Potential — Benchmark-Based Optimisation (Target = 2nd-Best Peer; all formulas dynamic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="55" customHeight="1">
+          <t>Cash Release Potential — AR | Inventory | AP — All formulas dynamic (Target = 2nd-Best Peer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Company</t>
@@ -3704,62 +4380,110 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Current
-AR ($M)</t>
+          <t>COGS
+($M)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Current
-DSO (days)</t>
+          <t>Current AR
+($M)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Target
-DSO (days)
+          <t>Current DSO
+(days)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Target DSO
 [=SMALL(…,2)]</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Target
-AR ($M)
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Target AR
 [=Rev÷365×TgtDSO]</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>AR Cash
-Release ($M)
-[=MAX(CurAR–TgtAR,0)]</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Current
-Inventory ($M)</t>
+Release
+[=MAX(AR–TgtAR,0)]</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Target
-DIO (days)
+          <t>Current Inv
+($M)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Current DIO
+(days)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Target DIO
 [=SMALL(…,2)]</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Target
-Inventory ($M)
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Target Inv
 [=COGS÷365×TgtDIO]</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Inv Cash
-Release ($M)
-[=MAX(CurInv–TgtInv,0)]</t>
+Release
+[=MAX(Inv–TgtInv,0)]</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Current AP
+($M)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Current DPO
+(days)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Target DPO
+[=LARGE(…,2)]</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Target AP
+[=COGS÷365×TgtDPO]</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>AP Cash
+Release
+[=MAX(TgtAP–AP,0)]
+(extend terms)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL Cash
+Release
+[=AR+Inv+AP]
+($M)</t>
         </is>
       </c>
     </row>
@@ -3769,7 +4493,7 @@
         <v/>
       </c>
       <c r="B3" s="5">
-        <f>Scoring_Ranking!H3</f>
+        <f>Scoring_Ranking!J3</f>
         <v/>
       </c>
       <c r="C3" s="4">
@@ -3777,49 +4501,81 @@
         <v/>
       </c>
       <c r="D3" s="4">
+        <f>Raw_Data!C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
         <f>Raw_Data!D3</f>
         <v/>
       </c>
-      <c r="E3" s="18">
+      <c r="F3" s="21">
         <f>Efficiency_Metrics!H3</f>
         <v/>
       </c>
-      <c r="F3" s="18">
+      <c r="G3" s="21">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G3" s="4">
-        <f>C3/365*F3</f>
-        <v/>
-      </c>
       <c r="H3" s="4">
-        <f>MAX(D3-G3,0)</f>
+        <f>C3/365*G3</f>
         <v/>
       </c>
       <c r="I3" s="4">
+        <f>MAX(E3-H3,0)</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
         <f>Raw_Data!E3</f>
         <v/>
       </c>
-      <c r="J3" s="18">
+      <c r="K3" s="21">
+        <f>Efficiency_Metrics!J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="21">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K3" s="4">
-        <f>Raw_Data!C3/365*J3</f>
-        <v/>
-      </c>
-      <c r="L3" s="4">
-        <f>MAX(I3-K3,0)</f>
+      <c r="M3" s="4">
+        <f>D3/365*L3</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>MAX(J3-M3,0)</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>Raw_Data!H3</f>
+        <v/>
+      </c>
+      <c r="P3" s="21">
+        <f>Efficiency_Metrics!L3</f>
+        <v/>
+      </c>
+      <c r="Q3" s="21">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R3" s="4">
+        <f>D3/365*Q3</f>
+        <v/>
+      </c>
+      <c r="S3" s="4">
+        <f>MAX(R3-O3,0)</f>
+        <v/>
+      </c>
+      <c r="T3" s="4">
+        <f>I3+N3+S3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <f>Raw_Data!A4</f>
         <v/>
       </c>
       <c r="B4" s="8">
-        <f>Scoring_Ranking!H4</f>
+        <f>Scoring_Ranking!J4</f>
         <v/>
       </c>
       <c r="C4" s="7">
@@ -3827,39 +4583,71 @@
         <v/>
       </c>
       <c r="D4" s="7">
+        <f>Raw_Data!C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="7">
         <f>Raw_Data!D4</f>
         <v/>
       </c>
-      <c r="E4" s="19">
+      <c r="F4" s="22">
         <f>Efficiency_Metrics!H4</f>
         <v/>
       </c>
-      <c r="F4" s="19">
+      <c r="G4" s="22">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G4" s="7">
-        <f>C4/365*F4</f>
-        <v/>
-      </c>
       <c r="H4" s="7">
-        <f>MAX(D4-G4,0)</f>
+        <f>C4/365*G4</f>
         <v/>
       </c>
       <c r="I4" s="7">
+        <f>MAX(E4-H4,0)</f>
+        <v/>
+      </c>
+      <c r="J4" s="7">
         <f>Raw_Data!E4</f>
         <v/>
       </c>
-      <c r="J4" s="19">
+      <c r="K4" s="22">
+        <f>Efficiency_Metrics!J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K4" s="7">
-        <f>Raw_Data!C4/365*J4</f>
-        <v/>
-      </c>
-      <c r="L4" s="7">
-        <f>MAX(I4-K4,0)</f>
+      <c r="M4" s="7">
+        <f>D4/365*L4</f>
+        <v/>
+      </c>
+      <c r="N4" s="7">
+        <f>MAX(J4-M4,0)</f>
+        <v/>
+      </c>
+      <c r="O4" s="7">
+        <f>Raw_Data!H4</f>
+        <v/>
+      </c>
+      <c r="P4" s="22">
+        <f>Efficiency_Metrics!L4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="22">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R4" s="7">
+        <f>D4/365*Q4</f>
+        <v/>
+      </c>
+      <c r="S4" s="7">
+        <f>MAX(R4-O4,0)</f>
+        <v/>
+      </c>
+      <c r="T4" s="7">
+        <f>I4+N4+S4</f>
         <v/>
       </c>
     </row>
@@ -3869,7 +4657,7 @@
         <v/>
       </c>
       <c r="B5" s="5">
-        <f>Scoring_Ranking!H5</f>
+        <f>Scoring_Ranking!J5</f>
         <v/>
       </c>
       <c r="C5" s="4">
@@ -3877,49 +4665,81 @@
         <v/>
       </c>
       <c r="D5" s="4">
+        <f>Raw_Data!C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
         <f>Raw_Data!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="F5" s="21">
         <f>Efficiency_Metrics!H5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="G5" s="21">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G5" s="4">
-        <f>C5/365*F5</f>
-        <v/>
-      </c>
       <c r="H5" s="4">
-        <f>MAX(D5-G5,0)</f>
+        <f>C5/365*G5</f>
         <v/>
       </c>
       <c r="I5" s="4">
+        <f>MAX(E5-H5,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
         <f>Raw_Data!E5</f>
         <v/>
       </c>
-      <c r="J5" s="18">
+      <c r="K5" s="21">
+        <f>Efficiency_Metrics!J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="21">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K5" s="4">
-        <f>Raw_Data!C5/365*J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="4">
-        <f>MAX(I5-K5,0)</f>
+      <c r="M5" s="4">
+        <f>D5/365*L5</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>MAX(J5-M5,0)</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>Raw_Data!H5</f>
+        <v/>
+      </c>
+      <c r="P5" s="21">
+        <f>Efficiency_Metrics!L5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="21">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R5" s="4">
+        <f>D5/365*Q5</f>
+        <v/>
+      </c>
+      <c r="S5" s="4">
+        <f>MAX(R5-O5,0)</f>
+        <v/>
+      </c>
+      <c r="T5" s="4">
+        <f>I5+N5+S5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <f>Raw_Data!A6</f>
         <v/>
       </c>
       <c r="B6" s="8">
-        <f>Scoring_Ranking!H6</f>
+        <f>Scoring_Ranking!J6</f>
         <v/>
       </c>
       <c r="C6" s="7">
@@ -3927,39 +4747,71 @@
         <v/>
       </c>
       <c r="D6" s="7">
+        <f>Raw_Data!C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="7">
         <f>Raw_Data!D6</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="F6" s="22">
         <f>Efficiency_Metrics!H6</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="G6" s="22">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G6" s="7">
-        <f>C6/365*F6</f>
-        <v/>
-      </c>
       <c r="H6" s="7">
-        <f>MAX(D6-G6,0)</f>
+        <f>C6/365*G6</f>
         <v/>
       </c>
       <c r="I6" s="7">
+        <f>MAX(E6-H6,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="7">
         <f>Raw_Data!E6</f>
         <v/>
       </c>
-      <c r="J6" s="19">
+      <c r="K6" s="22">
+        <f>Efficiency_Metrics!J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K6" s="7">
-        <f>Raw_Data!C6/365*J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="7">
-        <f>MAX(I6-K6,0)</f>
+      <c r="M6" s="7">
+        <f>D6/365*L6</f>
+        <v/>
+      </c>
+      <c r="N6" s="7">
+        <f>MAX(J6-M6,0)</f>
+        <v/>
+      </c>
+      <c r="O6" s="7">
+        <f>Raw_Data!H6</f>
+        <v/>
+      </c>
+      <c r="P6" s="22">
+        <f>Efficiency_Metrics!L6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="22">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R6" s="7">
+        <f>D6/365*Q6</f>
+        <v/>
+      </c>
+      <c r="S6" s="7">
+        <f>MAX(R6-O6,0)</f>
+        <v/>
+      </c>
+      <c r="T6" s="7">
+        <f>I6+N6+S6</f>
         <v/>
       </c>
     </row>
@@ -3969,7 +4821,7 @@
         <v/>
       </c>
       <c r="B7" s="5">
-        <f>Scoring_Ranking!H7</f>
+        <f>Scoring_Ranking!J7</f>
         <v/>
       </c>
       <c r="C7" s="4">
@@ -3977,49 +4829,81 @@
         <v/>
       </c>
       <c r="D7" s="4">
+        <f>Raw_Data!C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
         <f>Raw_Data!D7</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="F7" s="21">
         <f>Efficiency_Metrics!H7</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="G7" s="21">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G7" s="4">
-        <f>C7/365*F7</f>
-        <v/>
-      </c>
       <c r="H7" s="4">
-        <f>MAX(D7-G7,0)</f>
+        <f>C7/365*G7</f>
         <v/>
       </c>
       <c r="I7" s="4">
+        <f>MAX(E7-H7,0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
         <f>Raw_Data!E7</f>
         <v/>
       </c>
-      <c r="J7" s="18">
+      <c r="K7" s="21">
+        <f>Efficiency_Metrics!J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K7" s="4">
-        <f>Raw_Data!C7/365*J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="4">
-        <f>MAX(I7-K7,0)</f>
+      <c r="M7" s="4">
+        <f>D7/365*L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>MAX(J7-M7,0)</f>
+        <v/>
+      </c>
+      <c r="O7" s="4">
+        <f>Raw_Data!H7</f>
+        <v/>
+      </c>
+      <c r="P7" s="21">
+        <f>Efficiency_Metrics!L7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="21">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R7" s="4">
+        <f>D7/365*Q7</f>
+        <v/>
+      </c>
+      <c r="S7" s="4">
+        <f>MAX(R7-O7,0)</f>
+        <v/>
+      </c>
+      <c r="T7" s="4">
+        <f>I7+N7+S7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <f>Raw_Data!A8</f>
         <v/>
       </c>
       <c r="B8" s="8">
-        <f>Scoring_Ranking!H8</f>
+        <f>Scoring_Ranking!J8</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -4027,39 +4911,71 @@
         <v/>
       </c>
       <c r="D8" s="7">
+        <f>Raw_Data!C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="7">
         <f>Raw_Data!D8</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="F8" s="22">
         <f>Efficiency_Metrics!H8</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="G8" s="22">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G8" s="7">
-        <f>C8/365*F8</f>
-        <v/>
-      </c>
       <c r="H8" s="7">
-        <f>MAX(D8-G8,0)</f>
+        <f>C8/365*G8</f>
         <v/>
       </c>
       <c r="I8" s="7">
+        <f>MAX(E8-H8,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
         <f>Raw_Data!E8</f>
         <v/>
       </c>
-      <c r="J8" s="19">
+      <c r="K8" s="22">
+        <f>Efficiency_Metrics!J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="22">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K8" s="7">
-        <f>Raw_Data!C8/365*J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>MAX(I8-K8,0)</f>
+      <c r="M8" s="7">
+        <f>D8/365*L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>MAX(J8-M8,0)</f>
+        <v/>
+      </c>
+      <c r="O8" s="7">
+        <f>Raw_Data!H8</f>
+        <v/>
+      </c>
+      <c r="P8" s="22">
+        <f>Efficiency_Metrics!L8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="22">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R8" s="7">
+        <f>D8/365*Q8</f>
+        <v/>
+      </c>
+      <c r="S8" s="7">
+        <f>MAX(R8-O8,0)</f>
+        <v/>
+      </c>
+      <c r="T8" s="7">
+        <f>I8+N8+S8</f>
         <v/>
       </c>
     </row>
@@ -4069,7 +4985,7 @@
         <v/>
       </c>
       <c r="B9" s="5">
-        <f>Scoring_Ranking!H9</f>
+        <f>Scoring_Ranking!J9</f>
         <v/>
       </c>
       <c r="C9" s="4">
@@ -4077,49 +4993,81 @@
         <v/>
       </c>
       <c r="D9" s="4">
+        <f>Raw_Data!C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
         <f>Raw_Data!D9</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="F9" s="21">
         <f>Efficiency_Metrics!H9</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="G9" s="21">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G9" s="4">
-        <f>C9/365*F9</f>
-        <v/>
-      </c>
       <c r="H9" s="4">
-        <f>MAX(D9-G9,0)</f>
+        <f>C9/365*G9</f>
         <v/>
       </c>
       <c r="I9" s="4">
+        <f>MAX(E9-H9,0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
         <f>Raw_Data!E9</f>
         <v/>
       </c>
-      <c r="J9" s="18">
+      <c r="K9" s="21">
+        <f>Efficiency_Metrics!J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K9" s="4">
-        <f>Raw_Data!C9/365*J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="4">
-        <f>MAX(I9-K9,0)</f>
+      <c r="M9" s="4">
+        <f>D9/365*L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>MAX(J9-M9,0)</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>Raw_Data!H9</f>
+        <v/>
+      </c>
+      <c r="P9" s="21">
+        <f>Efficiency_Metrics!L9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="21">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R9" s="4">
+        <f>D9/365*Q9</f>
+        <v/>
+      </c>
+      <c r="S9" s="4">
+        <f>MAX(R9-O9,0)</f>
+        <v/>
+      </c>
+      <c r="T9" s="4">
+        <f>I9+N9+S9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <f>Raw_Data!A10</f>
         <v/>
       </c>
       <c r="B10" s="8">
-        <f>Scoring_Ranking!H10</f>
+        <f>Scoring_Ranking!J10</f>
         <v/>
       </c>
       <c r="C10" s="7">
@@ -4127,39 +5075,71 @@
         <v/>
       </c>
       <c r="D10" s="7">
+        <f>Raw_Data!C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="7">
         <f>Raw_Data!D10</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="F10" s="22">
         <f>Efficiency_Metrics!H10</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="G10" s="22">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G10" s="7">
-        <f>C10/365*F10</f>
-        <v/>
-      </c>
       <c r="H10" s="7">
-        <f>MAX(D10-G10,0)</f>
+        <f>C10/365*G10</f>
         <v/>
       </c>
       <c r="I10" s="7">
+        <f>MAX(E10-H10,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="7">
         <f>Raw_Data!E10</f>
         <v/>
       </c>
-      <c r="J10" s="19">
+      <c r="K10" s="22">
+        <f>Efficiency_Metrics!J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K10" s="7">
-        <f>Raw_Data!C10/365*J10</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>MAX(I10-K10,0)</f>
+      <c r="M10" s="7">
+        <f>D10/365*L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="7">
+        <f>MAX(J10-M10,0)</f>
+        <v/>
+      </c>
+      <c r="O10" s="7">
+        <f>Raw_Data!H10</f>
+        <v/>
+      </c>
+      <c r="P10" s="22">
+        <f>Efficiency_Metrics!L10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="22">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R10" s="7">
+        <f>D10/365*Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="7">
+        <f>MAX(R10-O10,0)</f>
+        <v/>
+      </c>
+      <c r="T10" s="7">
+        <f>I10+N10+S10</f>
         <v/>
       </c>
     </row>
@@ -4169,7 +5149,7 @@
         <v/>
       </c>
       <c r="B11" s="5">
-        <f>Scoring_Ranking!H11</f>
+        <f>Scoring_Ranking!J11</f>
         <v/>
       </c>
       <c r="C11" s="4">
@@ -4177,49 +5157,81 @@
         <v/>
       </c>
       <c r="D11" s="4">
+        <f>Raw_Data!C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="4">
         <f>Raw_Data!D11</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="F11" s="21">
         <f>Efficiency_Metrics!H11</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="G11" s="21">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G11" s="4">
-        <f>C11/365*F11</f>
-        <v/>
-      </c>
       <c r="H11" s="4">
-        <f>MAX(D11-G11,0)</f>
+        <f>C11/365*G11</f>
         <v/>
       </c>
       <c r="I11" s="4">
+        <f>MAX(E11-H11,0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
         <f>Raw_Data!E11</f>
         <v/>
       </c>
-      <c r="J11" s="18">
+      <c r="K11" s="21">
+        <f>Efficiency_Metrics!J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K11" s="4">
-        <f>Raw_Data!C11/365*J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="4">
-        <f>MAX(I11-K11,0)</f>
+      <c r="M11" s="4">
+        <f>D11/365*L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>MAX(J11-M11,0)</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>Raw_Data!H11</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>Efficiency_Metrics!L11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="21">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R11" s="4">
+        <f>D11/365*Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="4">
+        <f>MAX(R11-O11,0)</f>
+        <v/>
+      </c>
+      <c r="T11" s="4">
+        <f>I11+N11+S11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <f>Raw_Data!A12</f>
         <v/>
       </c>
       <c r="B12" s="8">
-        <f>Scoring_Ranking!H12</f>
+        <f>Scoring_Ranking!J12</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -4227,84 +5239,1382 @@
         <v/>
       </c>
       <c r="D12" s="7">
+        <f>Raw_Data!C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="7">
         <f>Raw_Data!D12</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="F12" s="22">
         <f>Efficiency_Metrics!H12</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="G12" s="22">
         <f>SMALL(Efficiency_Metrics!$H$3:Efficiency_Metrics!$H$12,2)</f>
         <v/>
       </c>
-      <c r="G12" s="7">
-        <f>C12/365*F12</f>
-        <v/>
-      </c>
       <c r="H12" s="7">
-        <f>MAX(D12-G12,0)</f>
+        <f>C12/365*G12</f>
         <v/>
       </c>
       <c r="I12" s="7">
+        <f>MAX(E12-H12,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="7">
         <f>Raw_Data!E12</f>
         <v/>
       </c>
-      <c r="J12" s="19">
+      <c r="K12" s="22">
+        <f>Efficiency_Metrics!J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
         <f>SMALL(Efficiency_Metrics!$J$3:Efficiency_Metrics!$J$12,2)</f>
         <v/>
       </c>
-      <c r="K12" s="7">
-        <f>Raw_Data!C12/365*J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="7">
-        <f>MAX(I12-K12,0)</f>
+      <c r="M12" s="7">
+        <f>D12/365*L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="7">
+        <f>MAX(J12-M12,0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="7">
+        <f>Raw_Data!H12</f>
+        <v/>
+      </c>
+      <c r="P12" s="22">
+        <f>Efficiency_Metrics!L12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="22">
+        <f>LARGE(Efficiency_Metrics!$L$3:Efficiency_Metrics!$L$12,2)</f>
+        <v/>
+      </c>
+      <c r="R12" s="7">
+        <f>D12/365*Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="7">
+        <f>MAX(R12-O12,0)</f>
+        <v/>
+      </c>
+      <c r="T12" s="7">
+        <f>I12+N12+S12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL — All 10 Companies (companies already at/below benchmark contribute $0):</t>
-        </is>
-      </c>
-      <c r="H14" s="21">
-        <f>SUM(H3:H12)</f>
-        <v/>
-      </c>
-      <c r="L14" s="21">
-        <f>SUM(L3:L12)</f>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL All 10 Companies (MAX(…,0) ensures below-target contributes $0):</t>
+        </is>
+      </c>
+      <c r="I14" s="24">
+        <f>SUM(I3:I12)</f>
+        <v/>
+      </c>
+      <c r="N14" s="24">
+        <f>SUM(N3:N12)</f>
+        <v/>
+      </c>
+      <c r="S14" s="24">
+        <f>SUM(S3:S12)</f>
+        <v/>
+      </c>
+      <c r="T14" s="24">
+        <f>SUM(T3:T12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22">
-        <f>CONCATENATE("TOTAL Q3+Q4 Companies: ",COUNTIF(B3:B12,"Q3")+COUNTIF(B3:B12,"Q4")," companies")</f>
-        <v/>
-      </c>
-      <c r="H15" s="23">
-        <f>SUMIF(B3:B12,"Q3",H3:H12)+SUMIF(B3:B12,"Q4",H3:H12)</f>
-        <v/>
-      </c>
-      <c r="L15" s="23">
-        <f>SUMIF(B3:B12,"Q3",L3:L12)+SUMIF(B3:B12,"Q4",L3:L12)</f>
+      <c r="A15" s="25">
+        <f>CONCATENATE("TOTAL Q3+Q4 Companies (",COUNTIF(B3:B12,"Q3")+COUNTIF(B3:B12,"Q4")," cos):  AR  |  Inv  |  AP  |  Combined")</f>
+        <v/>
+      </c>
+      <c r="I15" s="26">
+        <f>SUMIF(B3:B12,"Q3",I3:I12)+SUMIF(B3:B12,"Q4",I3:I12)</f>
+        <v/>
+      </c>
+      <c r="N15" s="26">
+        <f>SUMIF(B3:B12,"Q3",N3:N12)+SUMIF(B3:B12,"Q4",N3:N12)</f>
+        <v/>
+      </c>
+      <c r="S15" s="26">
+        <f>SUMIF(B3:B12,"Q3",S3:S12)+SUMIF(B3:B12,"Q4",S3:S12)</f>
+        <v/>
+      </c>
+      <c r="T15" s="26">
+        <f>SUMIF(B3:B12,"Q3",T3:T12)+SUMIF(B3:B12,"Q4",T3:T12)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Methodology: Target DSO = 2nd-lowest peer DSO [SMALL(...,2)] — avoids outlier distortion. Target DIO = 2nd-lowest peer DIO. Target Inventory = COGS÷365×Target DIO (COGS-based to be consistent). MAX(…,0) ensures companies already at benchmark show $0 (no negative release). All targets update automatically when Raw_Data changes.</t>
+          <t>Target DSO/DIO = SMALL(…,2) (2nd-best peer, avoids outlier).  Target DPO = LARGE(…,2) (2nd-highest peer).  AP Cash Release = positive gap when current DPO &lt; target DPO (company is paying suppliers too early).  MAX(…,0) ensures companies already at/beyond benchmark contribute $0.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A17:T17"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Semiconductor WC Benchmarking – Executive Dashboard (All values formula-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>SECTION A — Consolidated Metrics Per Company (all values pulled from analysis sheets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Overall
+Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Quartile</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>DSO
+(days)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>DIO
+(days)</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>DPO
+(days)</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>CCC
+(days)</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>AR Turns</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Inv Turns</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>CRR (%)</t>
+        </is>
+      </c>
+      <c r="K4" s="28" t="inlineStr">
+        <is>
+          <t>WC
+($M)</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>Op NWC
+($M)</t>
+        </is>
+      </c>
+      <c r="M4" s="28" t="inlineStr">
+        <is>
+          <t>WC/Rev
+(%)</t>
+        </is>
+      </c>
+      <c r="N4" s="28" t="inlineStr">
+        <is>
+          <t>NWC/Rev
+(%)</t>
+        </is>
+      </c>
+      <c r="O4" s="28" t="inlineStr">
+        <is>
+          <t>Current
+Ratio</t>
+        </is>
+      </c>
+      <c r="P4" s="28" t="inlineStr">
+        <is>
+          <t>Quick
+Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <f>Raw_Data!A3</f>
+        <v/>
+      </c>
+      <c r="B5" s="13">
+        <f>Scoring_Ranking!I3</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>Scoring_Ranking!J3</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>Efficiency_Metrics!H3</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>Efficiency_Metrics!J3</f>
+        <v/>
+      </c>
+      <c r="F5" s="21">
+        <f>Efficiency_Metrics!L3</f>
+        <v/>
+      </c>
+      <c r="G5" s="21">
+        <f>Efficiency_Metrics!M3</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>Efficiency_Metrics!I3</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>Efficiency_Metrics!K3</f>
+        <v/>
+      </c>
+      <c r="J5" s="11">
+        <f>Efficiency_Metrics!N3</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>WC_NWC!D3</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>WC_NWC!J3</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f>WC_NWC!F3</f>
+        <v/>
+      </c>
+      <c r="N5" s="11">
+        <f>WC_NWC!K3</f>
+        <v/>
+      </c>
+      <c r="O5" s="12">
+        <f>WC_NWC!L3</f>
+        <v/>
+      </c>
+      <c r="P5" s="12">
+        <f>WC_NWC!M3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>Raw_Data!A4</f>
+        <v/>
+      </c>
+      <c r="B6" s="17">
+        <f>Scoring_Ranking!I4</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>Scoring_Ranking!J4</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
+        <f>Efficiency_Metrics!H4</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>Efficiency_Metrics!J4</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>Efficiency_Metrics!L4</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>Efficiency_Metrics!M4</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>Efficiency_Metrics!I4</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>Efficiency_Metrics!K4</f>
+        <v/>
+      </c>
+      <c r="J6" s="15">
+        <f>Efficiency_Metrics!N4</f>
+        <v/>
+      </c>
+      <c r="K6" s="7">
+        <f>WC_NWC!D4</f>
+        <v/>
+      </c>
+      <c r="L6" s="7">
+        <f>WC_NWC!J4</f>
+        <v/>
+      </c>
+      <c r="M6" s="15">
+        <f>WC_NWC!F4</f>
+        <v/>
+      </c>
+      <c r="N6" s="15">
+        <f>WC_NWC!K4</f>
+        <v/>
+      </c>
+      <c r="O6" s="16">
+        <f>WC_NWC!L4</f>
+        <v/>
+      </c>
+      <c r="P6" s="16">
+        <f>WC_NWC!M4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <f>Raw_Data!A5</f>
+        <v/>
+      </c>
+      <c r="B7" s="13">
+        <f>Scoring_Ranking!I5</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>Scoring_Ranking!J5</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>Efficiency_Metrics!H5</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>Efficiency_Metrics!J5</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>Efficiency_Metrics!L5</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>Efficiency_Metrics!M5</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>Efficiency_Metrics!I5</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>Efficiency_Metrics!K5</f>
+        <v/>
+      </c>
+      <c r="J7" s="11">
+        <f>Efficiency_Metrics!N5</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>WC_NWC!D5</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>WC_NWC!J5</f>
+        <v/>
+      </c>
+      <c r="M7" s="11">
+        <f>WC_NWC!F5</f>
+        <v/>
+      </c>
+      <c r="N7" s="11">
+        <f>WC_NWC!K5</f>
+        <v/>
+      </c>
+      <c r="O7" s="12">
+        <f>WC_NWC!L5</f>
+        <v/>
+      </c>
+      <c r="P7" s="12">
+        <f>WC_NWC!M5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14">
+        <f>Raw_Data!A6</f>
+        <v/>
+      </c>
+      <c r="B8" s="17">
+        <f>Scoring_Ranking!I6</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>Scoring_Ranking!J6</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
+        <f>Efficiency_Metrics!H6</f>
+        <v/>
+      </c>
+      <c r="E8" s="22">
+        <f>Efficiency_Metrics!J6</f>
+        <v/>
+      </c>
+      <c r="F8" s="22">
+        <f>Efficiency_Metrics!L6</f>
+        <v/>
+      </c>
+      <c r="G8" s="22">
+        <f>Efficiency_Metrics!M6</f>
+        <v/>
+      </c>
+      <c r="H8" s="22">
+        <f>Efficiency_Metrics!I6</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>Efficiency_Metrics!K6</f>
+        <v/>
+      </c>
+      <c r="J8" s="15">
+        <f>Efficiency_Metrics!N6</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>WC_NWC!D6</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>WC_NWC!J6</f>
+        <v/>
+      </c>
+      <c r="M8" s="15">
+        <f>WC_NWC!F6</f>
+        <v/>
+      </c>
+      <c r="N8" s="15">
+        <f>WC_NWC!K6</f>
+        <v/>
+      </c>
+      <c r="O8" s="16">
+        <f>WC_NWC!L6</f>
+        <v/>
+      </c>
+      <c r="P8" s="16">
+        <f>WC_NWC!M6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <f>Raw_Data!A7</f>
+        <v/>
+      </c>
+      <c r="B9" s="13">
+        <f>Scoring_Ranking!I7</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>Scoring_Ranking!J7</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Efficiency_Metrics!H7</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Efficiency_Metrics!J7</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>Efficiency_Metrics!L7</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>Efficiency_Metrics!M7</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>Efficiency_Metrics!I7</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>Efficiency_Metrics!K7</f>
+        <v/>
+      </c>
+      <c r="J9" s="11">
+        <f>Efficiency_Metrics!N7</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>WC_NWC!D7</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>WC_NWC!J7</f>
+        <v/>
+      </c>
+      <c r="M9" s="11">
+        <f>WC_NWC!F7</f>
+        <v/>
+      </c>
+      <c r="N9" s="11">
+        <f>WC_NWC!K7</f>
+        <v/>
+      </c>
+      <c r="O9" s="12">
+        <f>WC_NWC!L7</f>
+        <v/>
+      </c>
+      <c r="P9" s="12">
+        <f>WC_NWC!M7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14">
+        <f>Raw_Data!A8</f>
+        <v/>
+      </c>
+      <c r="B10" s="17">
+        <f>Scoring_Ranking!I8</f>
+        <v/>
+      </c>
+      <c r="C10" s="8">
+        <f>Scoring_Ranking!J8</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>Efficiency_Metrics!H8</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>Efficiency_Metrics!J8</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>Efficiency_Metrics!L8</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>Efficiency_Metrics!M8</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>Efficiency_Metrics!I8</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>Efficiency_Metrics!K8</f>
+        <v/>
+      </c>
+      <c r="J10" s="15">
+        <f>Efficiency_Metrics!N8</f>
+        <v/>
+      </c>
+      <c r="K10" s="7">
+        <f>WC_NWC!D8</f>
+        <v/>
+      </c>
+      <c r="L10" s="7">
+        <f>WC_NWC!J8</f>
+        <v/>
+      </c>
+      <c r="M10" s="15">
+        <f>WC_NWC!F8</f>
+        <v/>
+      </c>
+      <c r="N10" s="15">
+        <f>WC_NWC!K8</f>
+        <v/>
+      </c>
+      <c r="O10" s="16">
+        <f>WC_NWC!L8</f>
+        <v/>
+      </c>
+      <c r="P10" s="16">
+        <f>WC_NWC!M8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <f>Raw_Data!A9</f>
+        <v/>
+      </c>
+      <c r="B11" s="13">
+        <f>Scoring_Ranking!I9</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>Scoring_Ranking!J9</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>Efficiency_Metrics!H9</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>Efficiency_Metrics!J9</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>Efficiency_Metrics!L9</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>Efficiency_Metrics!M9</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>Efficiency_Metrics!I9</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>Efficiency_Metrics!K9</f>
+        <v/>
+      </c>
+      <c r="J11" s="11">
+        <f>Efficiency_Metrics!N9</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>WC_NWC!D9</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>WC_NWC!J9</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>WC_NWC!F9</f>
+        <v/>
+      </c>
+      <c r="N11" s="11">
+        <f>WC_NWC!K9</f>
+        <v/>
+      </c>
+      <c r="O11" s="12">
+        <f>WC_NWC!L9</f>
+        <v/>
+      </c>
+      <c r="P11" s="12">
+        <f>WC_NWC!M9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14">
+        <f>Raw_Data!A10</f>
+        <v/>
+      </c>
+      <c r="B12" s="17">
+        <f>Scoring_Ranking!I10</f>
+        <v/>
+      </c>
+      <c r="C12" s="8">
+        <f>Scoring_Ranking!J10</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>Efficiency_Metrics!H10</f>
+        <v/>
+      </c>
+      <c r="E12" s="22">
+        <f>Efficiency_Metrics!J10</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>Efficiency_Metrics!L10</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>Efficiency_Metrics!M10</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>Efficiency_Metrics!I10</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>Efficiency_Metrics!K10</f>
+        <v/>
+      </c>
+      <c r="J12" s="15">
+        <f>Efficiency_Metrics!N10</f>
+        <v/>
+      </c>
+      <c r="K12" s="7">
+        <f>WC_NWC!D10</f>
+        <v/>
+      </c>
+      <c r="L12" s="7">
+        <f>WC_NWC!J10</f>
+        <v/>
+      </c>
+      <c r="M12" s="15">
+        <f>WC_NWC!F10</f>
+        <v/>
+      </c>
+      <c r="N12" s="15">
+        <f>WC_NWC!K10</f>
+        <v/>
+      </c>
+      <c r="O12" s="16">
+        <f>WC_NWC!L10</f>
+        <v/>
+      </c>
+      <c r="P12" s="16">
+        <f>WC_NWC!M10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <f>Raw_Data!A11</f>
+        <v/>
+      </c>
+      <c r="B13" s="13">
+        <f>Scoring_Ranking!I11</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>Scoring_Ranking!J11</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>Efficiency_Metrics!H11</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>Efficiency_Metrics!J11</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>Efficiency_Metrics!L11</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>Efficiency_Metrics!M11</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>Efficiency_Metrics!I11</f>
+        <v/>
+      </c>
+      <c r="I13" s="21">
+        <f>Efficiency_Metrics!K11</f>
+        <v/>
+      </c>
+      <c r="J13" s="11">
+        <f>Efficiency_Metrics!N11</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>WC_NWC!D11</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>WC_NWC!J11</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>WC_NWC!F11</f>
+        <v/>
+      </c>
+      <c r="N13" s="11">
+        <f>WC_NWC!K11</f>
+        <v/>
+      </c>
+      <c r="O13" s="12">
+        <f>WC_NWC!L11</f>
+        <v/>
+      </c>
+      <c r="P13" s="12">
+        <f>WC_NWC!M11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14">
+        <f>Raw_Data!A12</f>
+        <v/>
+      </c>
+      <c r="B14" s="17">
+        <f>Scoring_Ranking!I12</f>
+        <v/>
+      </c>
+      <c r="C14" s="8">
+        <f>Scoring_Ranking!J12</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>Efficiency_Metrics!H12</f>
+        <v/>
+      </c>
+      <c r="E14" s="22">
+        <f>Efficiency_Metrics!J12</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>Efficiency_Metrics!L12</f>
+        <v/>
+      </c>
+      <c r="G14" s="22">
+        <f>Efficiency_Metrics!M12</f>
+        <v/>
+      </c>
+      <c r="H14" s="22">
+        <f>Efficiency_Metrics!I12</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
+        <f>Efficiency_Metrics!K12</f>
+        <v/>
+      </c>
+      <c r="J14" s="15">
+        <f>Efficiency_Metrics!N12</f>
+        <v/>
+      </c>
+      <c r="K14" s="7">
+        <f>WC_NWC!D12</f>
+        <v/>
+      </c>
+      <c r="L14" s="7">
+        <f>WC_NWC!J12</f>
+        <v/>
+      </c>
+      <c r="M14" s="15">
+        <f>WC_NWC!F12</f>
+        <v/>
+      </c>
+      <c r="N14" s="15">
+        <f>WC_NWC!K12</f>
+        <v/>
+      </c>
+      <c r="O14" s="16">
+        <f>WC_NWC!L12</f>
+        <v/>
+      </c>
+      <c r="P14" s="16">
+        <f>WC_NWC!M12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>SECTION B — Peer Benchmark Summary (Best / Median / Worst — all formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Best-in-Class
+[formula]</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Peer Median
+[=MEDIAN]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Peer Average
+[=AVERAGE]</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Worst
+[formula]</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Benchmark
+Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>DSO (days)</t>
+        </is>
+      </c>
+      <c r="B18" s="22">
+        <f>MIN(Efficiency_Metrics!H3:Efficiency_Metrics!H12)</f>
+        <v/>
+      </c>
+      <c r="C18" s="22">
+        <f>MEDIAN(Efficiency_Metrics!H3:Efficiency_Metrics!H12)</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>AVERAGE(Efficiency_Metrics!H3:Efficiency_Metrics!H12)</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>MAX(Efficiency_Metrics!H3:Efficiency_Metrics!H12)</f>
+        <v/>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Lower = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>DIO (days)</t>
+        </is>
+      </c>
+      <c r="B19" s="21">
+        <f>MIN(Efficiency_Metrics!J3:Efficiency_Metrics!J12)</f>
+        <v/>
+      </c>
+      <c r="C19" s="21">
+        <f>MEDIAN(Efficiency_Metrics!J3:Efficiency_Metrics!J12)</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>AVERAGE(Efficiency_Metrics!J3:Efficiency_Metrics!J12)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>MAX(Efficiency_Metrics!J3:Efficiency_Metrics!J12)</f>
+        <v/>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Lower = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>DPO (days)</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>MAX(Efficiency_Metrics!L3:Efficiency_Metrics!L12)</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f>MEDIAN(Efficiency_Metrics!L3:Efficiency_Metrics!L12)</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>AVERAGE(Efficiency_Metrics!L3:Efficiency_Metrics!L12)</f>
+        <v/>
+      </c>
+      <c r="E20" s="22">
+        <f>MIN(Efficiency_Metrics!L3:Efficiency_Metrics!L12)</f>
+        <v/>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Higher = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>CCC (days)</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>MIN(Efficiency_Metrics!M3:Efficiency_Metrics!M12)</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>MEDIAN(Efficiency_Metrics!M3:Efficiency_Metrics!M12)</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>AVERAGE(Efficiency_Metrics!M3:Efficiency_Metrics!M12)</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>MAX(Efficiency_Metrics!M3:Efficiency_Metrics!M12)</f>
+        <v/>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Lower = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>AR Turns</t>
+        </is>
+      </c>
+      <c r="B22" s="22">
+        <f>MAX(Efficiency_Metrics!I3:Efficiency_Metrics!I12)</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f>MEDIAN(Efficiency_Metrics!I3:Efficiency_Metrics!I12)</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>AVERAGE(Efficiency_Metrics!I3:Efficiency_Metrics!I12)</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f>MIN(Efficiency_Metrics!I3:Efficiency_Metrics!I12)</f>
+        <v/>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Higher = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Inv Turns</t>
+        </is>
+      </c>
+      <c r="B23" s="21">
+        <f>MAX(Efficiency_Metrics!K3:Efficiency_Metrics!K12)</f>
+        <v/>
+      </c>
+      <c r="C23" s="21">
+        <f>MEDIAN(Efficiency_Metrics!K3:Efficiency_Metrics!K12)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>AVERAGE(Efficiency_Metrics!K3:Efficiency_Metrics!K12)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>MIN(Efficiency_Metrics!K3:Efficiency_Metrics!K12)</f>
+        <v/>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Higher = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>CRR (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>MAX(Efficiency_Metrics!N3:Efficiency_Metrics!N12)</f>
+        <v/>
+      </c>
+      <c r="C24" s="15">
+        <f>MEDIAN(Efficiency_Metrics!N3:Efficiency_Metrics!N12)</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>AVERAGE(Efficiency_Metrics!N3:Efficiency_Metrics!N12)</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
+        <f>MIN(Efficiency_Metrics!N3:Efficiency_Metrics!N12)</f>
+        <v/>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Higher = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>WC/Rev (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="11">
+        <f>MIN(WC_NWC!F3:WC_NWC!F12)</f>
+        <v/>
+      </c>
+      <c r="C25" s="11">
+        <f>MEDIAN(WC_NWC!F3:WC_NWC!F12)</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>AVERAGE(WC_NWC!F3:WC_NWC!F12)</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>MAX(WC_NWC!F3:WC_NWC!F12)</f>
+        <v/>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Lower = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>NWC/Rev (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="15">
+        <f>MIN(WC_NWC!K3:WC_NWC!K12)</f>
+        <v/>
+      </c>
+      <c r="C26" s="15">
+        <f>MEDIAN(WC_NWC!K3:WC_NWC!K12)</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>AVERAGE(WC_NWC!K3:WC_NWC!K12)</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>MAX(WC_NWC!K3:WC_NWC!K12)</f>
+        <v/>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Lower = Better</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Current Ratio</t>
+        </is>
+      </c>
+      <c r="B27" s="12">
+        <f>MAX(WC_NWC!L3:WC_NWC!L12)</f>
+        <v/>
+      </c>
+      <c r="C27" s="12">
+        <f>MEDIAN(WC_NWC!L3:WC_NWC!L12)</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>AVERAGE(WC_NWC!L3:WC_NWC!L12)</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>MIN(WC_NWC!L3:WC_NWC!L12)</f>
+        <v/>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>≥1 healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Quick Ratio</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>MAX(WC_NWC!M3:WC_NWC!M12)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>MEDIAN(WC_NWC!M3:WC_NWC!M12)</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>AVERAGE(WC_NWC!M3:WC_NWC!M12)</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>MIN(WC_NWC!M3:WC_NWC!M12)</f>
+        <v/>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>≥0.8 healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>SECTION C — Cash Release Potential Summary (all values from Cash_Release sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>AR Cash Release
+($M)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Inv Cash Release
+($M)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>AP Cash Release
+($M)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Total Cash Release
+($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>All 10 Companies</t>
+        </is>
+      </c>
+      <c r="B33" s="29">
+        <f>Cash_Release!I14</f>
+        <v/>
+      </c>
+      <c r="C33" s="29">
+        <f>Cash_Release!N14</f>
+        <v/>
+      </c>
+      <c r="D33" s="29">
+        <f>Cash_Release!S14</f>
+        <v/>
+      </c>
+      <c r="E33" s="29">
+        <f>Cash_Release!T14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Q3 + Q4 Laggards only</t>
+        </is>
+      </c>
+      <c r="B34" s="30">
+        <f>Cash_Release!I15</f>
+        <v/>
+      </c>
+      <c r="C34" s="30">
+        <f>Cash_Release!N15</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>Cash_Release!S15</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>Cash_Release!T15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>This dashboard is 100% formula-driven — every value references a source cell in Raw_Data, WC_NWC, Efficiency_Metrics, Scoring_Ranking, Benchmark_Analysis, or Cash_Release. Select any cell and inspect the formula bar to trace back to raw data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A16:P16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Semiconductor_WC_Benchmarking.xlsx
+++ b/Semiconductor_WC_Benchmarking.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Efficiency_Metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Scoring_Ranking" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Benchmark_Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cash_Release" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Charts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash_Release" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,10 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -107,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -121,11 +126,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +250,38 @@
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -291,6 +356,719 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cash Conversion Cycle (CCC) — Peer Comparison</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>CCC (days)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$E$4:$E$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Days</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>DSO vs DIO vs DPO — Working Capital Days Breakdown</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>DSO</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$4:$B$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>DIO</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$C$4:$C$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>DPO</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$D$4:$D$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Days</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>AR Turns vs Inventory Turns — Efficiency Comparison</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>AR Turns</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$F$4:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Inv Turns</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$G$4:$G$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Turns</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cash Release Potential by Component ($M)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>AR Release</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$L$4:$L$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Inv Release</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$M$4:$M$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>AP Release</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$N$4:$N$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$M</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Overall Rank — Composite Scorecard (1 = Best)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Overall Rank</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$K$4:$K$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Rank (lower=better)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1842,6 +2620,10 @@
           <t>Best-in-Class WC/Rev  →</t>
         </is>
       </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="32" t="n"/>
       <c r="F14" s="19">
         <f>MIN(F3:F12)</f>
         <v/>
@@ -1853,6 +2635,10 @@
           <t>Best-in-Class NWC/Rev →</t>
         </is>
       </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="32" t="n"/>
       <c r="K15" s="19">
         <f>MIN(K3:K12)</f>
         <v/>
@@ -1864,6 +2650,10 @@
           <t>Peer-Avg Current Ratio →</t>
         </is>
       </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="32" t="n"/>
       <c r="L16" s="20">
         <f>AVERAGE(L3:L12)</f>
         <v/>
@@ -1875,6 +2665,10 @@
           <t>Peer-Avg Quick Ratio   →</t>
         </is>
       </c>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="32" t="n"/>
       <c r="M17" s="20">
         <f>AVERAGE(M3:M12)</f>
         <v/>
@@ -1896,6 +2690,102 @@
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
+  <conditionalFormatting sqref="D3:D12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J12">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K12">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L12">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M12">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N12">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O12">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2798,6 +3688,12 @@
           <t>Best DSO (Min):</t>
         </is>
       </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="32" t="n"/>
       <c r="H14" s="23">
         <f>MIN(H3:H12)</f>
         <v/>
@@ -2809,6 +3705,12 @@
           <t>Best AR Turns (Max):</t>
         </is>
       </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="32" t="n"/>
       <c r="I15" s="23">
         <f>MAX(I3:I12)</f>
         <v/>
@@ -2820,6 +3722,12 @@
           <t>Best DIO (Min):</t>
         </is>
       </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="32" t="n"/>
       <c r="J16" s="23">
         <f>MIN(J3:J12)</f>
         <v/>
@@ -2831,6 +3739,12 @@
           <t>Best Inv Turns (Max):</t>
         </is>
       </c>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
       <c r="K17" s="23">
         <f>MAX(K3:K12)</f>
         <v/>
@@ -2842,6 +3756,12 @@
           <t>Best DPO (Max):</t>
         </is>
       </c>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="32" t="n"/>
       <c r="L18" s="23">
         <f>MAX(L3:L12)</f>
         <v/>
@@ -2853,6 +3773,12 @@
           <t>Best CCC (Min):</t>
         </is>
       </c>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
       <c r="M19" s="23">
         <f>MIN(M3:M12)</f>
         <v/>
@@ -2864,6 +3790,12 @@
           <t>Best CRR (Max):</t>
         </is>
       </c>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="32" t="n"/>
       <c r="N20" s="19">
         <f>MAX(N3:N12)</f>
         <v/>
@@ -2888,6 +3820,90 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
+  <conditionalFormatting sqref="H3:H12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J12">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K12">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L12">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M12">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N12">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3414,6 +4430,30 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A14:J14"/>
   </mergeCells>
+  <conditionalFormatting sqref="H3:H12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4319,11 +5359,818 @@
     <mergeCell ref="A14:R14"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3:F12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L12">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O12">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R12">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Semiconductor WC Benchmarking — Visual Analysis Charts (auto-refresh with source data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DSO
+(days)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DIO
+(days)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>DPO
+(days)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>CCC
+(days)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>AR Turns</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Inv Turns</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>CRR (%)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>WC/Rev (%)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NWC/Rev (%)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Overall Rank</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>AR Release
+($M)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Inv Release
+($M)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>AP Release
+($M)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Total Release
+($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33">
+        <f>Raw_Data!A3</f>
+        <v/>
+      </c>
+      <c r="B4" s="34">
+        <f>Efficiency_Metrics!H3</f>
+        <v/>
+      </c>
+      <c r="C4" s="34">
+        <f>Efficiency_Metrics!J3</f>
+        <v/>
+      </c>
+      <c r="D4" s="34">
+        <f>Efficiency_Metrics!L3</f>
+        <v/>
+      </c>
+      <c r="E4" s="34">
+        <f>Efficiency_Metrics!M3</f>
+        <v/>
+      </c>
+      <c r="F4" s="34">
+        <f>Efficiency_Metrics!I3</f>
+        <v/>
+      </c>
+      <c r="G4" s="34">
+        <f>Efficiency_Metrics!K3</f>
+        <v/>
+      </c>
+      <c r="H4" s="35">
+        <f>Efficiency_Metrics!N3</f>
+        <v/>
+      </c>
+      <c r="I4" s="35">
+        <f>WC_NWC!F3</f>
+        <v/>
+      </c>
+      <c r="J4" s="35">
+        <f>WC_NWC!K3</f>
+        <v/>
+      </c>
+      <c r="K4" s="36">
+        <f>Scoring_Ranking!I3</f>
+        <v/>
+      </c>
+      <c r="L4" s="37">
+        <f>Cash_Release!I3</f>
+        <v/>
+      </c>
+      <c r="M4" s="37">
+        <f>Cash_Release!N3</f>
+        <v/>
+      </c>
+      <c r="N4" s="37">
+        <f>Cash_Release!S3</f>
+        <v/>
+      </c>
+      <c r="O4" s="37">
+        <f>Cash_Release!T3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38">
+        <f>Raw_Data!A4</f>
+        <v/>
+      </c>
+      <c r="B5" s="39">
+        <f>Efficiency_Metrics!H4</f>
+        <v/>
+      </c>
+      <c r="C5" s="39">
+        <f>Efficiency_Metrics!J4</f>
+        <v/>
+      </c>
+      <c r="D5" s="39">
+        <f>Efficiency_Metrics!L4</f>
+        <v/>
+      </c>
+      <c r="E5" s="39">
+        <f>Efficiency_Metrics!M4</f>
+        <v/>
+      </c>
+      <c r="F5" s="39">
+        <f>Efficiency_Metrics!I4</f>
+        <v/>
+      </c>
+      <c r="G5" s="39">
+        <f>Efficiency_Metrics!K4</f>
+        <v/>
+      </c>
+      <c r="H5" s="40">
+        <f>Efficiency_Metrics!N4</f>
+        <v/>
+      </c>
+      <c r="I5" s="40">
+        <f>WC_NWC!F4</f>
+        <v/>
+      </c>
+      <c r="J5" s="40">
+        <f>WC_NWC!K4</f>
+        <v/>
+      </c>
+      <c r="K5" s="41">
+        <f>Scoring_Ranking!I4</f>
+        <v/>
+      </c>
+      <c r="L5" s="42">
+        <f>Cash_Release!I4</f>
+        <v/>
+      </c>
+      <c r="M5" s="42">
+        <f>Cash_Release!N4</f>
+        <v/>
+      </c>
+      <c r="N5" s="42">
+        <f>Cash_Release!S4</f>
+        <v/>
+      </c>
+      <c r="O5" s="42">
+        <f>Cash_Release!T4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33">
+        <f>Raw_Data!A5</f>
+        <v/>
+      </c>
+      <c r="B6" s="34">
+        <f>Efficiency_Metrics!H5</f>
+        <v/>
+      </c>
+      <c r="C6" s="34">
+        <f>Efficiency_Metrics!J5</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
+        <f>Efficiency_Metrics!L5</f>
+        <v/>
+      </c>
+      <c r="E6" s="34">
+        <f>Efficiency_Metrics!M5</f>
+        <v/>
+      </c>
+      <c r="F6" s="34">
+        <f>Efficiency_Metrics!I5</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>Efficiency_Metrics!K5</f>
+        <v/>
+      </c>
+      <c r="H6" s="35">
+        <f>Efficiency_Metrics!N5</f>
+        <v/>
+      </c>
+      <c r="I6" s="35">
+        <f>WC_NWC!F5</f>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f>WC_NWC!K5</f>
+        <v/>
+      </c>
+      <c r="K6" s="36">
+        <f>Scoring_Ranking!I5</f>
+        <v/>
+      </c>
+      <c r="L6" s="37">
+        <f>Cash_Release!I5</f>
+        <v/>
+      </c>
+      <c r="M6" s="37">
+        <f>Cash_Release!N5</f>
+        <v/>
+      </c>
+      <c r="N6" s="37">
+        <f>Cash_Release!S5</f>
+        <v/>
+      </c>
+      <c r="O6" s="37">
+        <f>Cash_Release!T5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38">
+        <f>Raw_Data!A6</f>
+        <v/>
+      </c>
+      <c r="B7" s="39">
+        <f>Efficiency_Metrics!H6</f>
+        <v/>
+      </c>
+      <c r="C7" s="39">
+        <f>Efficiency_Metrics!J6</f>
+        <v/>
+      </c>
+      <c r="D7" s="39">
+        <f>Efficiency_Metrics!L6</f>
+        <v/>
+      </c>
+      <c r="E7" s="39">
+        <f>Efficiency_Metrics!M6</f>
+        <v/>
+      </c>
+      <c r="F7" s="39">
+        <f>Efficiency_Metrics!I6</f>
+        <v/>
+      </c>
+      <c r="G7" s="39">
+        <f>Efficiency_Metrics!K6</f>
+        <v/>
+      </c>
+      <c r="H7" s="40">
+        <f>Efficiency_Metrics!N6</f>
+        <v/>
+      </c>
+      <c r="I7" s="40">
+        <f>WC_NWC!F6</f>
+        <v/>
+      </c>
+      <c r="J7" s="40">
+        <f>WC_NWC!K6</f>
+        <v/>
+      </c>
+      <c r="K7" s="41">
+        <f>Scoring_Ranking!I6</f>
+        <v/>
+      </c>
+      <c r="L7" s="42">
+        <f>Cash_Release!I6</f>
+        <v/>
+      </c>
+      <c r="M7" s="42">
+        <f>Cash_Release!N6</f>
+        <v/>
+      </c>
+      <c r="N7" s="42">
+        <f>Cash_Release!S6</f>
+        <v/>
+      </c>
+      <c r="O7" s="42">
+        <f>Cash_Release!T6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33">
+        <f>Raw_Data!A7</f>
+        <v/>
+      </c>
+      <c r="B8" s="34">
+        <f>Efficiency_Metrics!H7</f>
+        <v/>
+      </c>
+      <c r="C8" s="34">
+        <f>Efficiency_Metrics!J7</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>Efficiency_Metrics!L7</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>Efficiency_Metrics!M7</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>Efficiency_Metrics!I7</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>Efficiency_Metrics!K7</f>
+        <v/>
+      </c>
+      <c r="H8" s="35">
+        <f>Efficiency_Metrics!N7</f>
+        <v/>
+      </c>
+      <c r="I8" s="35">
+        <f>WC_NWC!F7</f>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f>WC_NWC!K7</f>
+        <v/>
+      </c>
+      <c r="K8" s="36">
+        <f>Scoring_Ranking!I7</f>
+        <v/>
+      </c>
+      <c r="L8" s="37">
+        <f>Cash_Release!I7</f>
+        <v/>
+      </c>
+      <c r="M8" s="37">
+        <f>Cash_Release!N7</f>
+        <v/>
+      </c>
+      <c r="N8" s="37">
+        <f>Cash_Release!S7</f>
+        <v/>
+      </c>
+      <c r="O8" s="37">
+        <f>Cash_Release!T7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38">
+        <f>Raw_Data!A8</f>
+        <v/>
+      </c>
+      <c r="B9" s="39">
+        <f>Efficiency_Metrics!H8</f>
+        <v/>
+      </c>
+      <c r="C9" s="39">
+        <f>Efficiency_Metrics!J8</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
+        <f>Efficiency_Metrics!L8</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>Efficiency_Metrics!M8</f>
+        <v/>
+      </c>
+      <c r="F9" s="39">
+        <f>Efficiency_Metrics!I8</f>
+        <v/>
+      </c>
+      <c r="G9" s="39">
+        <f>Efficiency_Metrics!K8</f>
+        <v/>
+      </c>
+      <c r="H9" s="40">
+        <f>Efficiency_Metrics!N8</f>
+        <v/>
+      </c>
+      <c r="I9" s="40">
+        <f>WC_NWC!F8</f>
+        <v/>
+      </c>
+      <c r="J9" s="40">
+        <f>WC_NWC!K8</f>
+        <v/>
+      </c>
+      <c r="K9" s="41">
+        <f>Scoring_Ranking!I8</f>
+        <v/>
+      </c>
+      <c r="L9" s="42">
+        <f>Cash_Release!I8</f>
+        <v/>
+      </c>
+      <c r="M9" s="42">
+        <f>Cash_Release!N8</f>
+        <v/>
+      </c>
+      <c r="N9" s="42">
+        <f>Cash_Release!S8</f>
+        <v/>
+      </c>
+      <c r="O9" s="42">
+        <f>Cash_Release!T8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33">
+        <f>Raw_Data!A9</f>
+        <v/>
+      </c>
+      <c r="B10" s="34">
+        <f>Efficiency_Metrics!H9</f>
+        <v/>
+      </c>
+      <c r="C10" s="34">
+        <f>Efficiency_Metrics!J9</f>
+        <v/>
+      </c>
+      <c r="D10" s="34">
+        <f>Efficiency_Metrics!L9</f>
+        <v/>
+      </c>
+      <c r="E10" s="34">
+        <f>Efficiency_Metrics!M9</f>
+        <v/>
+      </c>
+      <c r="F10" s="34">
+        <f>Efficiency_Metrics!I9</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>Efficiency_Metrics!K9</f>
+        <v/>
+      </c>
+      <c r="H10" s="35">
+        <f>Efficiency_Metrics!N9</f>
+        <v/>
+      </c>
+      <c r="I10" s="35">
+        <f>WC_NWC!F9</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>WC_NWC!K9</f>
+        <v/>
+      </c>
+      <c r="K10" s="36">
+        <f>Scoring_Ranking!I9</f>
+        <v/>
+      </c>
+      <c r="L10" s="37">
+        <f>Cash_Release!I9</f>
+        <v/>
+      </c>
+      <c r="M10" s="37">
+        <f>Cash_Release!N9</f>
+        <v/>
+      </c>
+      <c r="N10" s="37">
+        <f>Cash_Release!S9</f>
+        <v/>
+      </c>
+      <c r="O10" s="37">
+        <f>Cash_Release!T9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38">
+        <f>Raw_Data!A10</f>
+        <v/>
+      </c>
+      <c r="B11" s="39">
+        <f>Efficiency_Metrics!H10</f>
+        <v/>
+      </c>
+      <c r="C11" s="39">
+        <f>Efficiency_Metrics!J10</f>
+        <v/>
+      </c>
+      <c r="D11" s="39">
+        <f>Efficiency_Metrics!L10</f>
+        <v/>
+      </c>
+      <c r="E11" s="39">
+        <f>Efficiency_Metrics!M10</f>
+        <v/>
+      </c>
+      <c r="F11" s="39">
+        <f>Efficiency_Metrics!I10</f>
+        <v/>
+      </c>
+      <c r="G11" s="39">
+        <f>Efficiency_Metrics!K10</f>
+        <v/>
+      </c>
+      <c r="H11" s="40">
+        <f>Efficiency_Metrics!N10</f>
+        <v/>
+      </c>
+      <c r="I11" s="40">
+        <f>WC_NWC!F10</f>
+        <v/>
+      </c>
+      <c r="J11" s="40">
+        <f>WC_NWC!K10</f>
+        <v/>
+      </c>
+      <c r="K11" s="41">
+        <f>Scoring_Ranking!I10</f>
+        <v/>
+      </c>
+      <c r="L11" s="42">
+        <f>Cash_Release!I10</f>
+        <v/>
+      </c>
+      <c r="M11" s="42">
+        <f>Cash_Release!N10</f>
+        <v/>
+      </c>
+      <c r="N11" s="42">
+        <f>Cash_Release!S10</f>
+        <v/>
+      </c>
+      <c r="O11" s="42">
+        <f>Cash_Release!T10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33">
+        <f>Raw_Data!A11</f>
+        <v/>
+      </c>
+      <c r="B12" s="34">
+        <f>Efficiency_Metrics!H11</f>
+        <v/>
+      </c>
+      <c r="C12" s="34">
+        <f>Efficiency_Metrics!J11</f>
+        <v/>
+      </c>
+      <c r="D12" s="34">
+        <f>Efficiency_Metrics!L11</f>
+        <v/>
+      </c>
+      <c r="E12" s="34">
+        <f>Efficiency_Metrics!M11</f>
+        <v/>
+      </c>
+      <c r="F12" s="34">
+        <f>Efficiency_Metrics!I11</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>Efficiency_Metrics!K11</f>
+        <v/>
+      </c>
+      <c r="H12" s="35">
+        <f>Efficiency_Metrics!N11</f>
+        <v/>
+      </c>
+      <c r="I12" s="35">
+        <f>WC_NWC!F11</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>WC_NWC!K11</f>
+        <v/>
+      </c>
+      <c r="K12" s="36">
+        <f>Scoring_Ranking!I11</f>
+        <v/>
+      </c>
+      <c r="L12" s="37">
+        <f>Cash_Release!I11</f>
+        <v/>
+      </c>
+      <c r="M12" s="37">
+        <f>Cash_Release!N11</f>
+        <v/>
+      </c>
+      <c r="N12" s="37">
+        <f>Cash_Release!S11</f>
+        <v/>
+      </c>
+      <c r="O12" s="37">
+        <f>Cash_Release!T11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38">
+        <f>Raw_Data!A12</f>
+        <v/>
+      </c>
+      <c r="B13" s="39">
+        <f>Efficiency_Metrics!H12</f>
+        <v/>
+      </c>
+      <c r="C13" s="39">
+        <f>Efficiency_Metrics!J12</f>
+        <v/>
+      </c>
+      <c r="D13" s="39">
+        <f>Efficiency_Metrics!L12</f>
+        <v/>
+      </c>
+      <c r="E13" s="39">
+        <f>Efficiency_Metrics!M12</f>
+        <v/>
+      </c>
+      <c r="F13" s="39">
+        <f>Efficiency_Metrics!I12</f>
+        <v/>
+      </c>
+      <c r="G13" s="39">
+        <f>Efficiency_Metrics!K12</f>
+        <v/>
+      </c>
+      <c r="H13" s="40">
+        <f>Efficiency_Metrics!N12</f>
+        <v/>
+      </c>
+      <c r="I13" s="40">
+        <f>WC_NWC!F12</f>
+        <v/>
+      </c>
+      <c r="J13" s="40">
+        <f>WC_NWC!K12</f>
+        <v/>
+      </c>
+      <c r="K13" s="41">
+        <f>Scoring_Ranking!I12</f>
+        <v/>
+      </c>
+      <c r="L13" s="42">
+        <f>Cash_Release!I12</f>
+        <v/>
+      </c>
+      <c r="M13" s="42">
+        <f>Cash_Release!N12</f>
+        <v/>
+      </c>
+      <c r="N13" s="42">
+        <f>Cash_Release!S12</f>
+        <v/>
+      </c>
+      <c r="O13" s="42">
+        <f>Cash_Release!T12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5313,6 +7160,13 @@
           <t>TOTAL All 10 Companies (MAX(…,0) ensures below-target contributes $0):</t>
         </is>
       </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="32" t="n"/>
       <c r="I14" s="24">
         <f>SUM(I3:I12)</f>
         <v/>
@@ -5335,6 +7189,13 @@
         <f>CONCATENATE("TOTAL Q3+Q4 Companies (",COUNTIF(B3:B12,"Q3")+COUNTIF(B3:B12,"Q4")," cos):  AR  |  Inv  |  AP  |  Combined")</f>
         <v/>
       </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="32" t="n"/>
       <c r="I15" s="26">
         <f>SUMIF(B3:B12,"Q3",I3:I12)+SUMIF(B3:B12,"Q4",I3:I12)</f>
         <v/>
@@ -5366,11 +7227,59 @@
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A15:H15"/>
   </mergeCells>
+  <conditionalFormatting sqref="I3:I12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3:S12">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T3:T12">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5411,6 +7320,21 @@
           <t>SECTION A — Consolidated Metrics Per Company (all values pulled from analysis sheets)</t>
         </is>
       </c>
+      <c r="B3" s="31" t="n"/>
+      <c r="C3" s="31" t="n"/>
+      <c r="D3" s="31" t="n"/>
+      <c r="E3" s="31" t="n"/>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="31" t="n"/>
+      <c r="H3" s="31" t="n"/>
+      <c r="I3" s="31" t="n"/>
+      <c r="J3" s="31" t="n"/>
+      <c r="K3" s="31" t="n"/>
+      <c r="L3" s="31" t="n"/>
+      <c r="M3" s="31" t="n"/>
+      <c r="N3" s="31" t="n"/>
+      <c r="O3" s="31" t="n"/>
+      <c r="P3" s="32" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="28" t="inlineStr">
@@ -6171,6 +8095,21 @@
           <t>SECTION B — Peer Benchmark Summary (Best / Median / Worst — all formulas)</t>
         </is>
       </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n"/>
+      <c r="J16" s="31" t="n"/>
+      <c r="K16" s="31" t="n"/>
+      <c r="L16" s="31" t="n"/>
+      <c r="M16" s="31" t="n"/>
+      <c r="N16" s="31" t="n"/>
+      <c r="O16" s="31" t="n"/>
+      <c r="P16" s="32" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -6523,6 +8462,21 @@
           <t>SECTION C — Cash Release Potential Summary (all values from Cash_Release sheet)</t>
         </is>
       </c>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="31" t="n"/>
+      <c r="I31" s="31" t="n"/>
+      <c r="J31" s="31" t="n"/>
+      <c r="K31" s="31" t="n"/>
+      <c r="L31" s="31" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="32" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -6616,6 +8570,162 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A16:P16"/>
   </mergeCells>
+  <conditionalFormatting sqref="D5:D14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E14">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F14">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G14">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I14">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J14">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K14">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L14">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M14">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N14">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O14">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P14">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>